--- a/data_cache/excel/SEQUENT_historical.xlsx
+++ b/data_cache/excel/SEQUENT_historical.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:G302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,15 +429,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>traded_quantity</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delivery_quantity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>delivery_pct</t>
         </is>
@@ -446,1045 +456,7525 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>216.44</v>
+        <v>157.49</v>
       </c>
       <c r="C2" t="n">
-        <v>841439</v>
+        <v>157.49</v>
       </c>
       <c r="D2" t="n">
-        <v>366878</v>
+        <v>157.49</v>
       </c>
       <c r="E2" t="n">
-        <v>43.6</v>
+        <v>9217709</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3193955</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>214.79</v>
+        <v>163.55</v>
       </c>
       <c r="C3" t="n">
-        <v>617710</v>
+        <v>163.55</v>
       </c>
       <c r="D3" t="n">
-        <v>263559</v>
+        <v>163.55</v>
       </c>
       <c r="E3" t="n">
-        <v>42.67</v>
+        <v>20819583</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4382622</v>
+      </c>
+      <c r="G3" t="n">
+        <v>21.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>224.15</v>
+        <v>165.98</v>
       </c>
       <c r="C4" t="n">
-        <v>1555566</v>
+        <v>165.98</v>
       </c>
       <c r="D4" t="n">
-        <v>861194</v>
+        <v>165.98</v>
       </c>
       <c r="E4" t="n">
-        <v>55.36</v>
+        <v>4456350</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1432623</v>
+      </c>
+      <c r="G4" t="n">
+        <v>32.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>228.72</v>
+        <v>166.1</v>
       </c>
       <c r="C5" t="n">
-        <v>2476834</v>
+        <v>166.1</v>
       </c>
       <c r="D5" t="n">
-        <v>1124749</v>
+        <v>166.1</v>
       </c>
       <c r="E5" t="n">
-        <v>45.41</v>
+        <v>2635702</v>
+      </c>
+      <c r="F5" t="n">
+        <v>849302</v>
+      </c>
+      <c r="G5" t="n">
+        <v>32.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>238.21</v>
+        <v>166.82</v>
       </c>
       <c r="C6" t="n">
-        <v>2948023</v>
+        <v>166.82</v>
       </c>
       <c r="D6" t="n">
-        <v>1509580</v>
+        <v>166.82</v>
       </c>
       <c r="E6" t="n">
-        <v>51.21</v>
+        <v>3505933</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1102361</v>
+      </c>
+      <c r="G6" t="n">
+        <v>31.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>227.81</v>
+        <v>165.39</v>
       </c>
       <c r="C7" t="n">
-        <v>2451087</v>
+        <v>165.39</v>
       </c>
       <c r="D7" t="n">
-        <v>1237862</v>
+        <v>165.39</v>
       </c>
       <c r="E7" t="n">
-        <v>50.5</v>
+        <v>3394934</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1113779</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32.81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>229.08</v>
+        <v>167.89</v>
       </c>
       <c r="C8" t="n">
-        <v>2480648</v>
+        <v>167.89</v>
       </c>
       <c r="D8" t="n">
-        <v>1154154</v>
+        <v>167.89</v>
       </c>
       <c r="E8" t="n">
-        <v>46.53</v>
+        <v>2008754</v>
+      </c>
+      <c r="F8" t="n">
+        <v>772244</v>
+      </c>
+      <c r="G8" t="n">
+        <v>38.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>231.14</v>
+        <v>164.96</v>
       </c>
       <c r="C9" t="n">
-        <v>2886632</v>
+        <v>164.96</v>
       </c>
       <c r="D9" t="n">
-        <v>1282376</v>
+        <v>164.96</v>
       </c>
       <c r="E9" t="n">
-        <v>44.42</v>
+        <v>2088662</v>
+      </c>
+      <c r="F9" t="n">
+        <v>794800</v>
+      </c>
+      <c r="G9" t="n">
+        <v>38.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>247.56</v>
+        <v>159.83</v>
       </c>
       <c r="C10" t="n">
-        <v>9154480</v>
+        <v>159.83</v>
       </c>
       <c r="D10" t="n">
-        <v>3022703</v>
+        <v>159.83</v>
       </c>
       <c r="E10" t="n">
-        <v>33.02</v>
+        <v>1775492</v>
+      </c>
+      <c r="F10" t="n">
+        <v>703604</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252</v>
+        <v>163.63</v>
       </c>
       <c r="C11" t="n">
-        <v>9066508</v>
+        <v>163.63</v>
       </c>
       <c r="D11" t="n">
-        <v>2604658</v>
+        <v>163.63</v>
       </c>
       <c r="E11" t="n">
-        <v>28.73</v>
+        <v>1514983</v>
+      </c>
+      <c r="F11" t="n">
+        <v>532201</v>
+      </c>
+      <c r="G11" t="n">
+        <v>35.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>239.62</v>
+        <v>161.62</v>
       </c>
       <c r="C12" t="n">
-        <v>3552069</v>
+        <v>161.62</v>
       </c>
       <c r="D12" t="n">
-        <v>1158078</v>
+        <v>161.62</v>
       </c>
       <c r="E12" t="n">
-        <v>32.6</v>
+        <v>1141237</v>
+      </c>
+      <c r="F12" t="n">
+        <v>375883</v>
+      </c>
+      <c r="G12" t="n">
+        <v>32.94</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>238.73</v>
+        <v>168.25</v>
       </c>
       <c r="C13" t="n">
-        <v>1735545</v>
+        <v>168.25</v>
       </c>
       <c r="D13" t="n">
-        <v>514624</v>
+        <v>168.25</v>
       </c>
       <c r="E13" t="n">
-        <v>29.65</v>
+        <v>2264342</v>
+      </c>
+      <c r="F13" t="n">
+        <v>849768</v>
+      </c>
+      <c r="G13" t="n">
+        <v>37.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>221.99</v>
+        <v>177.08</v>
       </c>
       <c r="C14" t="n">
-        <v>1929671</v>
+        <v>177.08</v>
       </c>
       <c r="D14" t="n">
-        <v>810136</v>
+        <v>177.08</v>
       </c>
       <c r="E14" t="n">
-        <v>41.98</v>
+        <v>9977003</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2933517</v>
+      </c>
+      <c r="G14" t="n">
+        <v>29.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>221.96</v>
+        <v>176.16</v>
       </c>
       <c r="C15" t="n">
-        <v>1642377</v>
+        <v>176.16</v>
       </c>
       <c r="D15" t="n">
-        <v>639200</v>
+        <v>176.16</v>
       </c>
       <c r="E15" t="n">
-        <v>38.92</v>
+        <v>7879139</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2309599</v>
+      </c>
+      <c r="G15" t="n">
+        <v>29.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>219.28</v>
+        <v>173.66</v>
       </c>
       <c r="C16" t="n">
-        <v>1071708</v>
+        <v>173.66</v>
       </c>
       <c r="D16" t="n">
-        <v>514162</v>
+        <v>173.66</v>
       </c>
       <c r="E16" t="n">
-        <v>47.98</v>
+        <v>4944592</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1402506</v>
+      </c>
+      <c r="G16" t="n">
+        <v>28.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>226.39</v>
+        <v>176.01</v>
       </c>
       <c r="C17" t="n">
-        <v>3780583</v>
+        <v>176.01</v>
       </c>
       <c r="D17" t="n">
-        <v>1075410</v>
+        <v>176.01</v>
       </c>
       <c r="E17" t="n">
-        <v>28.45</v>
+        <v>3130942</v>
+      </c>
+      <c r="F17" t="n">
+        <v>762619</v>
+      </c>
+      <c r="G17" t="n">
+        <v>24.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>223.46</v>
+        <v>179.81</v>
       </c>
       <c r="C18" t="n">
-        <v>1211340</v>
+        <v>179.81</v>
       </c>
       <c r="D18" t="n">
-        <v>600124</v>
+        <v>179.81</v>
       </c>
       <c r="E18" t="n">
-        <v>49.54</v>
+        <v>3962442</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1467374</v>
+      </c>
+      <c r="G18" t="n">
+        <v>37.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>221.41</v>
+        <v>172.91</v>
       </c>
       <c r="C19" t="n">
-        <v>891227</v>
+        <v>172.91</v>
       </c>
       <c r="D19" t="n">
-        <v>357731</v>
+        <v>172.91</v>
       </c>
       <c r="E19" t="n">
-        <v>40.14</v>
+        <v>2479489</v>
+      </c>
+      <c r="F19" t="n">
+        <v>955505</v>
+      </c>
+      <c r="G19" t="n">
+        <v>38.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>216.12</v>
+        <v>174.72</v>
       </c>
       <c r="C20" t="n">
-        <v>1175482</v>
+        <v>174.72</v>
       </c>
       <c r="D20" t="n">
-        <v>549090</v>
+        <v>174.72</v>
       </c>
       <c r="E20" t="n">
-        <v>46.71</v>
+        <v>2777660</v>
+      </c>
+      <c r="F20" t="n">
+        <v>836488</v>
+      </c>
+      <c r="G20" t="n">
+        <v>30.11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>212.63</v>
+        <v>178.19</v>
       </c>
       <c r="C21" t="n">
-        <v>979077</v>
+        <v>178.19</v>
       </c>
       <c r="D21" t="n">
-        <v>519602</v>
+        <v>178.19</v>
       </c>
       <c r="E21" t="n">
-        <v>53.07</v>
+        <v>2182244</v>
+      </c>
+      <c r="F21" t="n">
+        <v>650071</v>
+      </c>
+      <c r="G21" t="n">
+        <v>29.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>207.43</v>
+        <v>178.02</v>
       </c>
       <c r="C22" t="n">
-        <v>1548561</v>
+        <v>178.02</v>
       </c>
       <c r="D22" t="n">
-        <v>803047</v>
+        <v>178.02</v>
       </c>
       <c r="E22" t="n">
-        <v>51.86</v>
+        <v>1667000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>593471</v>
+      </c>
+      <c r="G22" t="n">
+        <v>35.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>199.7</v>
+        <v>177.83</v>
       </c>
       <c r="C23" t="n">
-        <v>2136594</v>
+        <v>177.83</v>
       </c>
       <c r="D23" t="n">
-        <v>1172219</v>
+        <v>177.83</v>
       </c>
       <c r="E23" t="n">
-        <v>54.86</v>
+        <v>2821661</v>
+      </c>
+      <c r="F23" t="n">
+        <v>950596</v>
+      </c>
+      <c r="G23" t="n">
+        <v>33.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>195.19</v>
+        <v>177.85</v>
       </c>
       <c r="C24" t="n">
-        <v>1516493</v>
+        <v>177.85</v>
       </c>
       <c r="D24" t="n">
-        <v>683304</v>
+        <v>177.85</v>
       </c>
       <c r="E24" t="n">
-        <v>45.06</v>
+        <v>3726668</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1836541</v>
+      </c>
+      <c r="G24" t="n">
+        <v>49.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>203.51</v>
+        <v>172.56</v>
       </c>
       <c r="C25" t="n">
-        <v>1253435</v>
+        <v>172.56</v>
       </c>
       <c r="D25" t="n">
-        <v>408181</v>
+        <v>172.56</v>
       </c>
       <c r="E25" t="n">
-        <v>32.56</v>
+        <v>2053991</v>
+      </c>
+      <c r="F25" t="n">
+        <v>731046</v>
+      </c>
+      <c r="G25" t="n">
+        <v>35.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>200.69</v>
+        <v>173.44</v>
       </c>
       <c r="C26" t="n">
-        <v>717920</v>
+        <v>173.44</v>
       </c>
       <c r="D26" t="n">
-        <v>325534</v>
+        <v>173.44</v>
       </c>
       <c r="E26" t="n">
-        <v>45.34</v>
+        <v>1222105</v>
+      </c>
+      <c r="F26" t="n">
+        <v>371302</v>
+      </c>
+      <c r="G26" t="n">
+        <v>30.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>205.92</v>
+        <v>179.09</v>
       </c>
       <c r="C27" t="n">
-        <v>860520</v>
+        <v>179.09</v>
       </c>
       <c r="D27" t="n">
-        <v>300694</v>
+        <v>179.09</v>
       </c>
       <c r="E27" t="n">
-        <v>34.94</v>
+        <v>2385539</v>
+      </c>
+      <c r="F27" t="n">
+        <v>997534</v>
+      </c>
+      <c r="G27" t="n">
+        <v>41.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>209.68</v>
+        <v>191.35</v>
       </c>
       <c r="C28" t="n">
-        <v>957812</v>
+        <v>191.35</v>
       </c>
       <c r="D28" t="n">
-        <v>443640</v>
+        <v>191.35</v>
       </c>
       <c r="E28" t="n">
-        <v>46.32</v>
+        <v>8430675</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3719679</v>
+      </c>
+      <c r="G28" t="n">
+        <v>44.12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>210.68</v>
+        <v>189.44</v>
       </c>
       <c r="C29" t="n">
-        <v>572740</v>
+        <v>189.44</v>
       </c>
       <c r="D29" t="n">
-        <v>238535</v>
+        <v>189.44</v>
       </c>
       <c r="E29" t="n">
-        <v>41.65</v>
+        <v>5389101</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2509044</v>
+      </c>
+      <c r="G29" t="n">
+        <v>46.56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>210.68</v>
+        <v>191.43</v>
       </c>
       <c r="C30" t="n">
-        <v>507420</v>
+        <v>191.43</v>
       </c>
       <c r="D30" t="n">
-        <v>208445</v>
+        <v>191.43</v>
       </c>
       <c r="E30" t="n">
-        <v>41.08</v>
+        <v>10307303</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4086417</v>
+      </c>
+      <c r="G30" t="n">
+        <v>39.65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>211.3</v>
+        <v>217.28</v>
       </c>
       <c r="C31" t="n">
-        <v>755622</v>
+        <v>217.28</v>
       </c>
       <c r="D31" t="n">
-        <v>267538</v>
+        <v>217.28</v>
       </c>
       <c r="E31" t="n">
-        <v>35.41</v>
+        <v>59058970</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12869215</v>
+      </c>
+      <c r="G31" t="n">
+        <v>21.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>209.36</v>
+        <v>232.22</v>
       </c>
       <c r="C32" t="n">
-        <v>516336</v>
+        <v>232.22</v>
       </c>
       <c r="D32" t="n">
-        <v>215723</v>
+        <v>232.22</v>
       </c>
       <c r="E32" t="n">
-        <v>41.78</v>
+        <v>34665107</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5339356</v>
+      </c>
+      <c r="G32" t="n">
+        <v>15.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>210.32</v>
+        <v>225.29</v>
       </c>
       <c r="C33" t="n">
-        <v>611341</v>
+        <v>225.29</v>
       </c>
       <c r="D33" t="n">
-        <v>276297</v>
+        <v>225.29</v>
       </c>
       <c r="E33" t="n">
-        <v>45.2</v>
+        <v>12661501</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2146712</v>
+      </c>
+      <c r="G33" t="n">
+        <v>16.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>218.33</v>
+        <v>225.29</v>
       </c>
       <c r="C34" t="n">
-        <v>1670306</v>
+        <v>225.29</v>
       </c>
       <c r="D34" t="n">
-        <v>842957</v>
+        <v>225.29</v>
       </c>
       <c r="E34" t="n">
-        <v>50.47</v>
+        <v>12661501</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2146712</v>
+      </c>
+      <c r="G34" t="n">
+        <v>16.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>216.68</v>
+        <v>216.85</v>
       </c>
       <c r="C35" t="n">
-        <v>751785</v>
+        <v>216.85</v>
       </c>
       <c r="D35" t="n">
-        <v>350337</v>
+        <v>216.85</v>
       </c>
       <c r="E35" t="n">
-        <v>46.6</v>
+        <v>5011266</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1369253</v>
+      </c>
+      <c r="G35" t="n">
+        <v>27.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>213.86</v>
+        <v>207.31</v>
       </c>
       <c r="C36" t="n">
-        <v>430662</v>
+        <v>207.31</v>
       </c>
       <c r="D36" t="n">
-        <v>239231</v>
+        <v>207.31</v>
       </c>
       <c r="E36" t="n">
-        <v>55.55</v>
+        <v>4724949</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1646292</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>213.54</v>
+        <v>198.7</v>
       </c>
       <c r="C37" t="n">
-        <v>488886</v>
+        <v>198.7</v>
       </c>
       <c r="D37" t="n">
-        <v>239880</v>
+        <v>198.7</v>
       </c>
       <c r="E37" t="n">
-        <v>49.07</v>
+        <v>5050312</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1844177</v>
+      </c>
+      <c r="G37" t="n">
+        <v>36.52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>209.28</v>
+        <v>175.86</v>
       </c>
       <c r="C38" t="n">
-        <v>355232</v>
+        <v>175.86</v>
       </c>
       <c r="D38" t="n">
-        <v>196485</v>
+        <v>175.86</v>
       </c>
       <c r="E38" t="n">
-        <v>55.31</v>
+        <v>306332</v>
+      </c>
+      <c r="F38" t="n">
+        <v>200069</v>
+      </c>
+      <c r="G38" t="n">
+        <v>65.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>206.4</v>
+        <v>184.65</v>
       </c>
       <c r="C39" t="n">
-        <v>716611</v>
+        <v>184.65</v>
       </c>
       <c r="D39" t="n">
-        <v>378643</v>
+        <v>184.65</v>
       </c>
       <c r="E39" t="n">
-        <v>52.84</v>
+        <v>257379</v>
+      </c>
+      <c r="F39" t="n">
+        <v>174599</v>
+      </c>
+      <c r="G39" t="n">
+        <v>67.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>208.54</v>
+        <v>193.88</v>
       </c>
       <c r="C40" t="n">
-        <v>474989</v>
+        <v>193.88</v>
       </c>
       <c r="D40" t="n">
-        <v>272827</v>
+        <v>193.88</v>
       </c>
       <c r="E40" t="n">
-        <v>57.44</v>
+        <v>822047</v>
+      </c>
+      <c r="F40" t="n">
+        <v>420228</v>
+      </c>
+      <c r="G40" t="n">
+        <v>51.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>208.38</v>
+        <v>203.57</v>
       </c>
       <c r="C41" t="n">
-        <v>397312</v>
+        <v>203.57</v>
       </c>
       <c r="D41" t="n">
-        <v>206774</v>
+        <v>203.57</v>
       </c>
       <c r="E41" t="n">
-        <v>52.04</v>
+        <v>627199</v>
+      </c>
+      <c r="F41" t="n">
+        <v>438145</v>
+      </c>
+      <c r="G41" t="n">
+        <v>69.86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>210.49</v>
+        <v>194.09</v>
       </c>
       <c r="C42" t="n">
-        <v>519743</v>
+        <v>194.09</v>
       </c>
       <c r="D42" t="n">
-        <v>276796</v>
+        <v>194.09</v>
       </c>
       <c r="E42" t="n">
-        <v>53.26</v>
+        <v>2149774</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1281903</v>
+      </c>
+      <c r="G42" t="n">
+        <v>59.63</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>206.94</v>
+        <v>196.63</v>
       </c>
       <c r="C43" t="n">
-        <v>527547</v>
+        <v>196.63</v>
       </c>
       <c r="D43" t="n">
-        <v>263643</v>
+        <v>196.63</v>
       </c>
       <c r="E43" t="n">
-        <v>49.98</v>
+        <v>689871</v>
+      </c>
+      <c r="F43" t="n">
+        <v>319190</v>
+      </c>
+      <c r="G43" t="n">
+        <v>46.27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>206.93</v>
+        <v>192.69</v>
       </c>
       <c r="C44" t="n">
-        <v>387550</v>
+        <v>192.69</v>
       </c>
       <c r="D44" t="n">
-        <v>161867</v>
+        <v>192.69</v>
       </c>
       <c r="E44" t="n">
-        <v>41.77</v>
+        <v>390698</v>
+      </c>
+      <c r="F44" t="n">
+        <v>192921</v>
+      </c>
+      <c r="G44" t="n">
+        <v>49.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>209.08</v>
+        <v>186.42</v>
       </c>
       <c r="C45" t="n">
-        <v>334428</v>
+        <v>186.42</v>
       </c>
       <c r="D45" t="n">
-        <v>161122</v>
+        <v>186.42</v>
       </c>
       <c r="E45" t="n">
-        <v>48.18</v>
+        <v>275879</v>
+      </c>
+      <c r="F45" t="n">
+        <v>156331</v>
+      </c>
+      <c r="G45" t="n">
+        <v>56.67</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>199.95</v>
+        <v>177.68</v>
       </c>
       <c r="C46" t="n">
-        <v>893761</v>
+        <v>177.68</v>
       </c>
       <c r="D46" t="n">
-        <v>492934</v>
+        <v>177.68</v>
       </c>
       <c r="E46" t="n">
-        <v>55.15</v>
+        <v>451054</v>
+      </c>
+      <c r="F46" t="n">
+        <v>239971</v>
+      </c>
+      <c r="G46" t="n">
+        <v>53.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>198.57</v>
+        <v>170.58</v>
       </c>
       <c r="C47" t="n">
-        <v>991803</v>
+        <v>170.58</v>
       </c>
       <c r="D47" t="n">
-        <v>384138</v>
+        <v>170.58</v>
       </c>
       <c r="E47" t="n">
-        <v>38.73</v>
+        <v>589992</v>
+      </c>
+      <c r="F47" t="n">
+        <v>252138</v>
+      </c>
+      <c r="G47" t="n">
+        <v>42.74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>192.49</v>
+        <v>178.89</v>
       </c>
       <c r="C48" t="n">
-        <v>724809</v>
+        <v>178.89</v>
       </c>
       <c r="D48" t="n">
-        <v>285906</v>
+        <v>178.89</v>
       </c>
       <c r="E48" t="n">
-        <v>39.45</v>
+        <v>692001</v>
+      </c>
+      <c r="F48" t="n">
+        <v>405635</v>
+      </c>
+      <c r="G48" t="n">
+        <v>58.62</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>190.05</v>
+        <v>175.01</v>
       </c>
       <c r="C49" t="n">
-        <v>447390</v>
+        <v>175.01</v>
       </c>
       <c r="D49" t="n">
-        <v>203654</v>
+        <v>175.01</v>
       </c>
       <c r="E49" t="n">
-        <v>45.52</v>
+        <v>388317</v>
+      </c>
+      <c r="F49" t="n">
+        <v>204840</v>
+      </c>
+      <c r="G49" t="n">
+        <v>52.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>192.57</v>
+        <v>176.47</v>
       </c>
       <c r="C50" t="n">
-        <v>449490</v>
+        <v>176.47</v>
       </c>
       <c r="D50" t="n">
-        <v>188757</v>
+        <v>176.47</v>
       </c>
       <c r="E50" t="n">
-        <v>41.99</v>
+        <v>450518</v>
+      </c>
+      <c r="F50" t="n">
+        <v>362972</v>
+      </c>
+      <c r="G50" t="n">
+        <v>80.56999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>192.57</v>
+        <v>173.15</v>
       </c>
       <c r="C51" t="n">
-        <v>449490</v>
+        <v>173.15</v>
       </c>
       <c r="D51" t="n">
-        <v>188757</v>
+        <v>173.15</v>
       </c>
       <c r="E51" t="n">
-        <v>41.99</v>
+        <v>248299</v>
+      </c>
+      <c r="F51" t="n">
+        <v>153002</v>
+      </c>
+      <c r="G51" t="n">
+        <v>61.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>193.73</v>
+        <v>181.48</v>
       </c>
       <c r="C52" t="n">
-        <v>409145</v>
+        <v>181.48</v>
       </c>
       <c r="D52" t="n">
-        <v>204113</v>
+        <v>181.48</v>
       </c>
       <c r="E52" t="n">
-        <v>49.89</v>
+        <v>773091</v>
+      </c>
+      <c r="F52" t="n">
+        <v>545168</v>
+      </c>
+      <c r="G52" t="n">
+        <v>70.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>205.68</v>
+        <v>177.11</v>
       </c>
       <c r="C53" t="n">
-        <v>2376238</v>
+        <v>177.11</v>
       </c>
       <c r="D53" t="n">
-        <v>799205</v>
+        <v>177.11</v>
       </c>
       <c r="E53" t="n">
-        <v>33.63</v>
+        <v>838999</v>
+      </c>
+      <c r="F53" t="n">
+        <v>380303</v>
+      </c>
+      <c r="G53" t="n">
+        <v>45.33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>199.43</v>
+        <v>177.36</v>
       </c>
       <c r="C54" t="n">
-        <v>894187</v>
+        <v>177.36</v>
       </c>
       <c r="D54" t="n">
-        <v>407786</v>
+        <v>177.36</v>
       </c>
       <c r="E54" t="n">
-        <v>45.6</v>
+        <v>681657</v>
+      </c>
+      <c r="F54" t="n">
+        <v>209255</v>
+      </c>
+      <c r="G54" t="n">
+        <v>30.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>193.98</v>
+        <v>176.82</v>
       </c>
       <c r="C55" t="n">
-        <v>681135</v>
+        <v>176.82</v>
       </c>
       <c r="D55" t="n">
-        <v>260617</v>
+        <v>176.82</v>
       </c>
       <c r="E55" t="n">
-        <v>38.26</v>
+        <v>320928</v>
+      </c>
+      <c r="F55" t="n">
+        <v>149857</v>
+      </c>
+      <c r="G55" t="n">
+        <v>46.69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>171.56</v>
+      </c>
+      <c r="C56" t="n">
+        <v>171.56</v>
+      </c>
+      <c r="D56" t="n">
+        <v>171.56</v>
+      </c>
+      <c r="E56" t="n">
+        <v>256070</v>
+      </c>
+      <c r="F56" t="n">
+        <v>134090</v>
+      </c>
+      <c r="G56" t="n">
+        <v>52.36</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>163</v>
+      </c>
+      <c r="C57" t="n">
+        <v>163</v>
+      </c>
+      <c r="D57" t="n">
+        <v>163</v>
+      </c>
+      <c r="E57" t="n">
+        <v>369473</v>
+      </c>
+      <c r="F57" t="n">
+        <v>204410</v>
+      </c>
+      <c r="G57" t="n">
+        <v>55.32</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>155.82</v>
+      </c>
+      <c r="C58" t="n">
+        <v>155.82</v>
+      </c>
+      <c r="D58" t="n">
+        <v>155.82</v>
+      </c>
+      <c r="E58" t="n">
+        <v>483758</v>
+      </c>
+      <c r="F58" t="n">
+        <v>253754</v>
+      </c>
+      <c r="G58" t="n">
+        <v>52.45</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>161.89</v>
+      </c>
+      <c r="C59" t="n">
+        <v>161.89</v>
+      </c>
+      <c r="D59" t="n">
+        <v>161.89</v>
+      </c>
+      <c r="E59" t="n">
+        <v>489190</v>
+      </c>
+      <c r="F59" t="n">
+        <v>244991</v>
+      </c>
+      <c r="G59" t="n">
+        <v>50.08</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>163.28</v>
+      </c>
+      <c r="C60" t="n">
+        <v>163.28</v>
+      </c>
+      <c r="D60" t="n">
+        <v>163.28</v>
+      </c>
+      <c r="E60" t="n">
+        <v>458069</v>
+      </c>
+      <c r="F60" t="n">
+        <v>243794</v>
+      </c>
+      <c r="G60" t="n">
+        <v>53.22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>165.13</v>
+      </c>
+      <c r="C61" t="n">
+        <v>165.13</v>
+      </c>
+      <c r="D61" t="n">
+        <v>165.13</v>
+      </c>
+      <c r="E61" t="n">
+        <v>295147</v>
+      </c>
+      <c r="F61" t="n">
+        <v>166123</v>
+      </c>
+      <c r="G61" t="n">
+        <v>56.28</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>160.17</v>
+      </c>
+      <c r="C62" t="n">
+        <v>160.17</v>
+      </c>
+      <c r="D62" t="n">
+        <v>160.17</v>
+      </c>
+      <c r="E62" t="n">
+        <v>242584</v>
+      </c>
+      <c r="F62" t="n">
+        <v>118948</v>
+      </c>
+      <c r="G62" t="n">
+        <v>49.03</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>163.74</v>
+      </c>
+      <c r="C63" t="n">
+        <v>163.74</v>
+      </c>
+      <c r="D63" t="n">
+        <v>163.74</v>
+      </c>
+      <c r="E63" t="n">
+        <v>206684</v>
+      </c>
+      <c r="F63" t="n">
+        <v>112976</v>
+      </c>
+      <c r="G63" t="n">
+        <v>54.66</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>164.36</v>
+      </c>
+      <c r="C64" t="n">
+        <v>164.36</v>
+      </c>
+      <c r="D64" t="n">
+        <v>164.36</v>
+      </c>
+      <c r="E64" t="n">
+        <v>290380</v>
+      </c>
+      <c r="F64" t="n">
+        <v>186544</v>
+      </c>
+      <c r="G64" t="n">
+        <v>64.23999999999999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>163.02</v>
+      </c>
+      <c r="C65" t="n">
+        <v>163.02</v>
+      </c>
+      <c r="D65" t="n">
+        <v>163.02</v>
+      </c>
+      <c r="E65" t="n">
+        <v>255735</v>
+      </c>
+      <c r="F65" t="n">
+        <v>140249</v>
+      </c>
+      <c r="G65" t="n">
+        <v>54.84</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>390210</v>
+      </c>
+      <c r="F66" t="n">
+        <v>267054</v>
+      </c>
+      <c r="G66" t="n">
+        <v>68.44</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>156.58</v>
+      </c>
+      <c r="C67" t="n">
+        <v>156.58</v>
+      </c>
+      <c r="D67" t="n">
+        <v>156.58</v>
+      </c>
+      <c r="E67" t="n">
+        <v>269835</v>
+      </c>
+      <c r="F67" t="n">
+        <v>181937</v>
+      </c>
+      <c r="G67" t="n">
+        <v>67.43000000000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>151.87</v>
+      </c>
+      <c r="C68" t="n">
+        <v>151.87</v>
+      </c>
+      <c r="D68" t="n">
+        <v>151.87</v>
+      </c>
+      <c r="E68" t="n">
+        <v>583058</v>
+      </c>
+      <c r="F68" t="n">
+        <v>214588</v>
+      </c>
+      <c r="G68" t="n">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>151.74</v>
+      </c>
+      <c r="C69" t="n">
+        <v>151.74</v>
+      </c>
+      <c r="D69" t="n">
+        <v>151.74</v>
+      </c>
+      <c r="E69" t="n">
+        <v>926439</v>
+      </c>
+      <c r="F69" t="n">
+        <v>404271</v>
+      </c>
+      <c r="G69" t="n">
+        <v>43.64</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>157.71</v>
+      </c>
+      <c r="C70" t="n">
+        <v>157.71</v>
+      </c>
+      <c r="D70" t="n">
+        <v>157.71</v>
+      </c>
+      <c r="E70" t="n">
+        <v>739299</v>
+      </c>
+      <c r="F70" t="n">
+        <v>247430</v>
+      </c>
+      <c r="G70" t="n">
+        <v>33.47</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>146.52</v>
+      </c>
+      <c r="C71" t="n">
+        <v>146.52</v>
+      </c>
+      <c r="D71" t="n">
+        <v>146.52</v>
+      </c>
+      <c r="E71" t="n">
+        <v>495635</v>
+      </c>
+      <c r="F71" t="n">
+        <v>208775</v>
+      </c>
+      <c r="G71" t="n">
+        <v>42.12</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>150.77</v>
+      </c>
+      <c r="C72" t="n">
+        <v>150.77</v>
+      </c>
+      <c r="D72" t="n">
+        <v>150.77</v>
+      </c>
+      <c r="E72" t="n">
+        <v>463588</v>
+      </c>
+      <c r="F72" t="n">
+        <v>228823</v>
+      </c>
+      <c r="G72" t="n">
+        <v>49.36</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>147.79</v>
+      </c>
+      <c r="C73" t="n">
+        <v>147.79</v>
+      </c>
+      <c r="D73" t="n">
+        <v>147.79</v>
+      </c>
+      <c r="E73" t="n">
+        <v>433226</v>
+      </c>
+      <c r="F73" t="n">
+        <v>230270</v>
+      </c>
+      <c r="G73" t="n">
+        <v>53.15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>150.08</v>
+      </c>
+      <c r="C74" t="n">
+        <v>150.08</v>
+      </c>
+      <c r="D74" t="n">
+        <v>150.08</v>
+      </c>
+      <c r="E74" t="n">
+        <v>428543</v>
+      </c>
+      <c r="F74" t="n">
+        <v>173236</v>
+      </c>
+      <c r="G74" t="n">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>158.71</v>
+      </c>
+      <c r="C75" t="n">
+        <v>158.71</v>
+      </c>
+      <c r="D75" t="n">
+        <v>158.71</v>
+      </c>
+      <c r="E75" t="n">
+        <v>596442</v>
+      </c>
+      <c r="F75" t="n">
+        <v>359700</v>
+      </c>
+      <c r="G75" t="n">
+        <v>60.31</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>159.51</v>
+      </c>
+      <c r="C76" t="n">
+        <v>159.51</v>
+      </c>
+      <c r="D76" t="n">
+        <v>159.51</v>
+      </c>
+      <c r="E76" t="n">
+        <v>385144</v>
+      </c>
+      <c r="F76" t="n">
+        <v>208325</v>
+      </c>
+      <c r="G76" t="n">
+        <v>54.09</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>156.12</v>
+      </c>
+      <c r="C77" t="n">
+        <v>156.12</v>
+      </c>
+      <c r="D77" t="n">
+        <v>156.12</v>
+      </c>
+      <c r="E77" t="n">
+        <v>282008</v>
+      </c>
+      <c r="F77" t="n">
+        <v>158410</v>
+      </c>
+      <c r="G77" t="n">
+        <v>56.17</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>157.46</v>
+      </c>
+      <c r="C78" t="n">
+        <v>157.46</v>
+      </c>
+      <c r="D78" t="n">
+        <v>157.46</v>
+      </c>
+      <c r="E78" t="n">
+        <v>410836</v>
+      </c>
+      <c r="F78" t="n">
+        <v>171550</v>
+      </c>
+      <c r="G78" t="n">
+        <v>41.76</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>151.12</v>
+      </c>
+      <c r="C79" t="n">
+        <v>151.12</v>
+      </c>
+      <c r="D79" t="n">
+        <v>151.12</v>
+      </c>
+      <c r="E79" t="n">
+        <v>287586</v>
+      </c>
+      <c r="F79" t="n">
+        <v>155818</v>
+      </c>
+      <c r="G79" t="n">
+        <v>54.18</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>148.61</v>
+      </c>
+      <c r="C80" t="n">
+        <v>148.61</v>
+      </c>
+      <c r="D80" t="n">
+        <v>148.61</v>
+      </c>
+      <c r="E80" t="n">
+        <v>550225</v>
+      </c>
+      <c r="F80" t="n">
+        <v>385945</v>
+      </c>
+      <c r="G80" t="n">
+        <v>70.14</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="C81" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="D81" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="E81" t="n">
+        <v>489985</v>
+      </c>
+      <c r="F81" t="n">
+        <v>216188</v>
+      </c>
+      <c r="G81" t="n">
+        <v>44.12</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>146.68</v>
+      </c>
+      <c r="C82" t="n">
+        <v>146.68</v>
+      </c>
+      <c r="D82" t="n">
+        <v>146.68</v>
+      </c>
+      <c r="E82" t="n">
+        <v>936434</v>
+      </c>
+      <c r="F82" t="n">
+        <v>585994</v>
+      </c>
+      <c r="G82" t="n">
+        <v>62.58</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>152.05</v>
+      </c>
+      <c r="C83" t="n">
+        <v>152.05</v>
+      </c>
+      <c r="D83" t="n">
+        <v>152.05</v>
+      </c>
+      <c r="E83" t="n">
+        <v>383851</v>
+      </c>
+      <c r="F83" t="n">
+        <v>167214</v>
+      </c>
+      <c r="G83" t="n">
+        <v>43.56</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>154.83</v>
+      </c>
+      <c r="C84" t="n">
+        <v>154.83</v>
+      </c>
+      <c r="D84" t="n">
+        <v>154.83</v>
+      </c>
+      <c r="E84" t="n">
+        <v>384438</v>
+      </c>
+      <c r="F84" t="n">
+        <v>183307</v>
+      </c>
+      <c r="G84" t="n">
+        <v>47.68</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>155.35</v>
+      </c>
+      <c r="C85" t="n">
+        <v>155.35</v>
+      </c>
+      <c r="D85" t="n">
+        <v>155.35</v>
+      </c>
+      <c r="E85" t="n">
+        <v>356819</v>
+      </c>
+      <c r="F85" t="n">
+        <v>161709</v>
+      </c>
+      <c r="G85" t="n">
+        <v>45.32</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>144.77</v>
+      </c>
+      <c r="C86" t="n">
+        <v>144.77</v>
+      </c>
+      <c r="D86" t="n">
+        <v>144.77</v>
+      </c>
+      <c r="E86" t="n">
+        <v>438194</v>
+      </c>
+      <c r="F86" t="n">
+        <v>247141</v>
+      </c>
+      <c r="G86" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>142.81</v>
+      </c>
+      <c r="C87" t="n">
+        <v>142.81</v>
+      </c>
+      <c r="D87" t="n">
+        <v>142.81</v>
+      </c>
+      <c r="E87" t="n">
+        <v>562792</v>
+      </c>
+      <c r="F87" t="n">
+        <v>360202</v>
+      </c>
+      <c r="G87" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>141.33</v>
+      </c>
+      <c r="C88" t="n">
+        <v>141.33</v>
+      </c>
+      <c r="D88" t="n">
+        <v>141.33</v>
+      </c>
+      <c r="E88" t="n">
+        <v>418649</v>
+      </c>
+      <c r="F88" t="n">
+        <v>287769</v>
+      </c>
+      <c r="G88" t="n">
+        <v>68.73999999999999</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>136.22</v>
+      </c>
+      <c r="C89" t="n">
+        <v>136.22</v>
+      </c>
+      <c r="D89" t="n">
+        <v>136.22</v>
+      </c>
+      <c r="E89" t="n">
+        <v>555043</v>
+      </c>
+      <c r="F89" t="n">
+        <v>292031</v>
+      </c>
+      <c r="G89" t="n">
+        <v>52.61</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>131.12</v>
+      </c>
+      <c r="C90" t="n">
+        <v>131.12</v>
+      </c>
+      <c r="D90" t="n">
+        <v>131.12</v>
+      </c>
+      <c r="E90" t="n">
+        <v>865083</v>
+      </c>
+      <c r="F90" t="n">
+        <v>566655</v>
+      </c>
+      <c r="G90" t="n">
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>139.18</v>
+      </c>
+      <c r="C91" t="n">
+        <v>139.18</v>
+      </c>
+      <c r="D91" t="n">
+        <v>139.18</v>
+      </c>
+      <c r="E91" t="n">
+        <v>737390</v>
+      </c>
+      <c r="F91" t="n">
+        <v>403226</v>
+      </c>
+      <c r="G91" t="n">
+        <v>54.68</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>144.56</v>
+      </c>
+      <c r="C92" t="n">
+        <v>144.56</v>
+      </c>
+      <c r="D92" t="n">
+        <v>144.56</v>
+      </c>
+      <c r="E92" t="n">
+        <v>693894</v>
+      </c>
+      <c r="F92" t="n">
+        <v>391535</v>
+      </c>
+      <c r="G92" t="n">
+        <v>56.43</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>143.36</v>
+      </c>
+      <c r="C93" t="n">
+        <v>143.36</v>
+      </c>
+      <c r="D93" t="n">
+        <v>143.36</v>
+      </c>
+      <c r="E93" t="n">
+        <v>496979</v>
+      </c>
+      <c r="F93" t="n">
+        <v>327758</v>
+      </c>
+      <c r="G93" t="n">
+        <v>65.95</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="C94" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="D94" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="E94" t="n">
+        <v>546943</v>
+      </c>
+      <c r="F94" t="n">
+        <v>310289</v>
+      </c>
+      <c r="G94" t="n">
+        <v>56.73</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>144.85</v>
+      </c>
+      <c r="C95" t="n">
+        <v>144.85</v>
+      </c>
+      <c r="D95" t="n">
+        <v>144.85</v>
+      </c>
+      <c r="E95" t="n">
+        <v>680248</v>
+      </c>
+      <c r="F95" t="n">
+        <v>420302</v>
+      </c>
+      <c r="G95" t="n">
+        <v>61.79</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>136.79</v>
+      </c>
+      <c r="C96" t="n">
+        <v>136.79</v>
+      </c>
+      <c r="D96" t="n">
+        <v>136.79</v>
+      </c>
+      <c r="E96" t="n">
+        <v>879495</v>
+      </c>
+      <c r="F96" t="n">
+        <v>482463</v>
+      </c>
+      <c r="G96" t="n">
+        <v>54.86</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>133.45</v>
+      </c>
+      <c r="C97" t="n">
+        <v>133.45</v>
+      </c>
+      <c r="D97" t="n">
+        <v>133.45</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1068340</v>
+      </c>
+      <c r="F97" t="n">
+        <v>466419</v>
+      </c>
+      <c r="G97" t="n">
+        <v>43.66</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>132.79</v>
+      </c>
+      <c r="C98" t="n">
+        <v>132.79</v>
+      </c>
+      <c r="D98" t="n">
+        <v>132.79</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1594059</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1027956</v>
+      </c>
+      <c r="G98" t="n">
+        <v>64.48999999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>130.82</v>
+      </c>
+      <c r="C99" t="n">
+        <v>130.82</v>
+      </c>
+      <c r="D99" t="n">
+        <v>130.82</v>
+      </c>
+      <c r="E99" t="n">
+        <v>744993</v>
+      </c>
+      <c r="F99" t="n">
+        <v>423522</v>
+      </c>
+      <c r="G99" t="n">
+        <v>56.85</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>135.81</v>
+      </c>
+      <c r="C100" t="n">
+        <v>135.81</v>
+      </c>
+      <c r="D100" t="n">
+        <v>135.81</v>
+      </c>
+      <c r="E100" t="n">
+        <v>540676</v>
+      </c>
+      <c r="F100" t="n">
+        <v>206149</v>
+      </c>
+      <c r="G100" t="n">
+        <v>38.13</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>137.13</v>
+      </c>
+      <c r="C101" t="n">
+        <v>137.13</v>
+      </c>
+      <c r="D101" t="n">
+        <v>137.13</v>
+      </c>
+      <c r="E101" t="n">
+        <v>509217</v>
+      </c>
+      <c r="F101" t="n">
+        <v>250839</v>
+      </c>
+      <c r="G101" t="n">
+        <v>49.26</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>142.68</v>
+      </c>
+      <c r="C102" t="n">
+        <v>142.68</v>
+      </c>
+      <c r="D102" t="n">
+        <v>142.68</v>
+      </c>
+      <c r="E102" t="n">
+        <v>633917</v>
+      </c>
+      <c r="F102" t="n">
+        <v>238431</v>
+      </c>
+      <c r="G102" t="n">
+        <v>37.61</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>133.77</v>
+      </c>
+      <c r="C103" t="n">
+        <v>133.77</v>
+      </c>
+      <c r="D103" t="n">
+        <v>133.77</v>
+      </c>
+      <c r="E103" t="n">
+        <v>674202</v>
+      </c>
+      <c r="F103" t="n">
+        <v>222042</v>
+      </c>
+      <c r="G103" t="n">
+        <v>32.93</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>126.68</v>
+      </c>
+      <c r="C104" t="n">
+        <v>126.68</v>
+      </c>
+      <c r="D104" t="n">
+        <v>126.68</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1344907</v>
+      </c>
+      <c r="F104" t="n">
+        <v>498720</v>
+      </c>
+      <c r="G104" t="n">
+        <v>37.08</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>136.92</v>
+      </c>
+      <c r="C105" t="n">
+        <v>136.92</v>
+      </c>
+      <c r="D105" t="n">
+        <v>136.92</v>
+      </c>
+      <c r="E105" t="n">
+        <v>955235</v>
+      </c>
+      <c r="F105" t="n">
+        <v>286062</v>
+      </c>
+      <c r="G105" t="n">
+        <v>29.95</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>132.09</v>
+      </c>
+      <c r="C106" t="n">
+        <v>132.09</v>
+      </c>
+      <c r="D106" t="n">
+        <v>132.09</v>
+      </c>
+      <c r="E106" t="n">
+        <v>400354</v>
+      </c>
+      <c r="F106" t="n">
+        <v>195961</v>
+      </c>
+      <c r="G106" t="n">
+        <v>48.95</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>137.18</v>
+      </c>
+      <c r="C107" t="n">
+        <v>137.18</v>
+      </c>
+      <c r="D107" t="n">
+        <v>137.18</v>
+      </c>
+      <c r="E107" t="n">
+        <v>536337</v>
+      </c>
+      <c r="F107" t="n">
+        <v>200690</v>
+      </c>
+      <c r="G107" t="n">
+        <v>37.42</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>144.11</v>
+      </c>
+      <c r="C108" t="n">
+        <v>144.11</v>
+      </c>
+      <c r="D108" t="n">
+        <v>144.11</v>
+      </c>
+      <c r="E108" t="n">
+        <v>683813</v>
+      </c>
+      <c r="F108" t="n">
+        <v>232408</v>
+      </c>
+      <c r="G108" t="n">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>145.02</v>
+      </c>
+      <c r="C109" t="n">
+        <v>145.02</v>
+      </c>
+      <c r="D109" t="n">
+        <v>145.02</v>
+      </c>
+      <c r="E109" t="n">
+        <v>635352</v>
+      </c>
+      <c r="F109" t="n">
+        <v>338600</v>
+      </c>
+      <c r="G109" t="n">
+        <v>53.29</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>147.34</v>
+      </c>
+      <c r="C110" t="n">
+        <v>147.34</v>
+      </c>
+      <c r="D110" t="n">
+        <v>147.34</v>
+      </c>
+      <c r="E110" t="n">
+        <v>955411</v>
+      </c>
+      <c r="F110" t="n">
+        <v>413870</v>
+      </c>
+      <c r="G110" t="n">
+        <v>43.32</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>148.17</v>
+      </c>
+      <c r="C111" t="n">
+        <v>148.17</v>
+      </c>
+      <c r="D111" t="n">
+        <v>148.17</v>
+      </c>
+      <c r="E111" t="n">
+        <v>532288</v>
+      </c>
+      <c r="F111" t="n">
+        <v>211533</v>
+      </c>
+      <c r="G111" t="n">
+        <v>39.74</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>146.23</v>
+      </c>
+      <c r="C112" t="n">
+        <v>146.23</v>
+      </c>
+      <c r="D112" t="n">
+        <v>146.23</v>
+      </c>
+      <c r="E112" t="n">
+        <v>278205</v>
+      </c>
+      <c r="F112" t="n">
+        <v>132708</v>
+      </c>
+      <c r="G112" t="n">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>148.72</v>
+      </c>
+      <c r="C113" t="n">
+        <v>148.72</v>
+      </c>
+      <c r="D113" t="n">
+        <v>148.72</v>
+      </c>
+      <c r="E113" t="n">
+        <v>395869</v>
+      </c>
+      <c r="F113" t="n">
+        <v>171551</v>
+      </c>
+      <c r="G113" t="n">
+        <v>43.34</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>154.04</v>
+      </c>
+      <c r="C114" t="n">
+        <v>154.04</v>
+      </c>
+      <c r="D114" t="n">
+        <v>154.04</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1240015</v>
+      </c>
+      <c r="F114" t="n">
+        <v>476187</v>
+      </c>
+      <c r="G114" t="n">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>148.12</v>
+      </c>
+      <c r="C115" t="n">
+        <v>148.12</v>
+      </c>
+      <c r="D115" t="n">
+        <v>148.12</v>
+      </c>
+      <c r="E115" t="n">
+        <v>656813</v>
+      </c>
+      <c r="F115" t="n">
+        <v>318495</v>
+      </c>
+      <c r="G115" t="n">
+        <v>48.49</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>150.12</v>
+      </c>
+      <c r="C116" t="n">
+        <v>150.12</v>
+      </c>
+      <c r="D116" t="n">
+        <v>150.12</v>
+      </c>
+      <c r="E116" t="n">
+        <v>402268</v>
+      </c>
+      <c r="F116" t="n">
+        <v>158965</v>
+      </c>
+      <c r="G116" t="n">
+        <v>39.52</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>147.38</v>
+      </c>
+      <c r="C117" t="n">
+        <v>147.38</v>
+      </c>
+      <c r="D117" t="n">
+        <v>147.38</v>
+      </c>
+      <c r="E117" t="n">
+        <v>402558</v>
+      </c>
+      <c r="F117" t="n">
+        <v>161910</v>
+      </c>
+      <c r="G117" t="n">
+        <v>40.22</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="C118" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>345447</v>
+      </c>
+      <c r="F118" t="n">
+        <v>149227</v>
+      </c>
+      <c r="G118" t="n">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>143.21</v>
+      </c>
+      <c r="C119" t="n">
+        <v>143.21</v>
+      </c>
+      <c r="D119" t="n">
+        <v>143.21</v>
+      </c>
+      <c r="E119" t="n">
+        <v>396460</v>
+      </c>
+      <c r="F119" t="n">
+        <v>162272</v>
+      </c>
+      <c r="G119" t="n">
+        <v>40.93</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>156.33</v>
+      </c>
+      <c r="C120" t="n">
+        <v>156.33</v>
+      </c>
+      <c r="D120" t="n">
+        <v>156.33</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2395271</v>
+      </c>
+      <c r="F120" t="n">
+        <v>577281</v>
+      </c>
+      <c r="G120" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>153.15</v>
+      </c>
+      <c r="C121" t="n">
+        <v>153.15</v>
+      </c>
+      <c r="D121" t="n">
+        <v>153.15</v>
+      </c>
+      <c r="E121" t="n">
+        <v>725716</v>
+      </c>
+      <c r="F121" t="n">
+        <v>342741</v>
+      </c>
+      <c r="G121" t="n">
+        <v>47.23</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="C122" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="D122" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="E122" t="n">
+        <v>572282</v>
+      </c>
+      <c r="F122" t="n">
+        <v>224195</v>
+      </c>
+      <c r="G122" t="n">
+        <v>39.18</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>155.16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>155.16</v>
+      </c>
+      <c r="D123" t="n">
+        <v>155.16</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1630376</v>
+      </c>
+      <c r="F123" t="n">
+        <v>552701</v>
+      </c>
+      <c r="G123" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>161.13</v>
+      </c>
+      <c r="C124" t="n">
+        <v>161.13</v>
+      </c>
+      <c r="D124" t="n">
+        <v>161.13</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1484320</v>
+      </c>
+      <c r="F124" t="n">
+        <v>506872</v>
+      </c>
+      <c r="G124" t="n">
+        <v>34.15</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>169.22</v>
+      </c>
+      <c r="C125" t="n">
+        <v>169.22</v>
+      </c>
+      <c r="D125" t="n">
+        <v>169.22</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1063832</v>
+      </c>
+      <c r="F125" t="n">
+        <v>412802</v>
+      </c>
+      <c r="G125" t="n">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>167.52</v>
+      </c>
+      <c r="C126" t="n">
+        <v>167.52</v>
+      </c>
+      <c r="D126" t="n">
+        <v>167.52</v>
+      </c>
+      <c r="E126" t="n">
+        <v>966949</v>
+      </c>
+      <c r="F126" t="n">
+        <v>391572</v>
+      </c>
+      <c r="G126" t="n">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>174.34</v>
+      </c>
+      <c r="C127" t="n">
+        <v>174.34</v>
+      </c>
+      <c r="D127" t="n">
+        <v>174.34</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1074307</v>
+      </c>
+      <c r="F127" t="n">
+        <v>395498</v>
+      </c>
+      <c r="G127" t="n">
+        <v>36.81</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>176.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>176.34</v>
+      </c>
+      <c r="D128" t="n">
+        <v>176.34</v>
+      </c>
+      <c r="E128" t="n">
+        <v>964776</v>
+      </c>
+      <c r="F128" t="n">
+        <v>412638</v>
+      </c>
+      <c r="G128" t="n">
+        <v>42.77</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>181.92</v>
+      </c>
+      <c r="C129" t="n">
+        <v>181.92</v>
+      </c>
+      <c r="D129" t="n">
+        <v>181.92</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2275667</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1132956</v>
+      </c>
+      <c r="G129" t="n">
+        <v>49.79</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>177.29</v>
+      </c>
+      <c r="C130" t="n">
+        <v>177.29</v>
+      </c>
+      <c r="D130" t="n">
+        <v>177.29</v>
+      </c>
+      <c r="E130" t="n">
+        <v>879530</v>
+      </c>
+      <c r="F130" t="n">
+        <v>522859</v>
+      </c>
+      <c r="G130" t="n">
+        <v>59.45</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>169.39</v>
+      </c>
+      <c r="C131" t="n">
+        <v>169.39</v>
+      </c>
+      <c r="D131" t="n">
+        <v>169.39</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2967960</v>
+      </c>
+      <c r="F131" t="n">
+        <v>921499</v>
+      </c>
+      <c r="G131" t="n">
+        <v>31.05</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>178.73</v>
+      </c>
+      <c r="C132" t="n">
+        <v>178.73</v>
+      </c>
+      <c r="D132" t="n">
+        <v>178.73</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2475616</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1164722</v>
+      </c>
+      <c r="G132" t="n">
+        <v>47.05</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>180.09</v>
+      </c>
+      <c r="C133" t="n">
+        <v>180.09</v>
+      </c>
+      <c r="D133" t="n">
+        <v>180.09</v>
+      </c>
+      <c r="E133" t="n">
+        <v>736088</v>
+      </c>
+      <c r="F133" t="n">
+        <v>315488</v>
+      </c>
+      <c r="G133" t="n">
+        <v>42.86</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>179.93</v>
+      </c>
+      <c r="C134" t="n">
+        <v>179.93</v>
+      </c>
+      <c r="D134" t="n">
+        <v>179.93</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1487841</v>
+      </c>
+      <c r="F134" t="n">
+        <v>703464</v>
+      </c>
+      <c r="G134" t="n">
+        <v>47.28</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="C135" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="D135" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="E135" t="n">
+        <v>653191</v>
+      </c>
+      <c r="F135" t="n">
+        <v>358656</v>
+      </c>
+      <c r="G135" t="n">
+        <v>54.91</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>196.08</v>
+      </c>
+      <c r="C136" t="n">
+        <v>196.08</v>
+      </c>
+      <c r="D136" t="n">
+        <v>196.08</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2696633</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1265916</v>
+      </c>
+      <c r="G136" t="n">
+        <v>46.94</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>185.98</v>
+      </c>
+      <c r="C137" t="n">
+        <v>185.98</v>
+      </c>
+      <c r="D137" t="n">
+        <v>185.98</v>
+      </c>
+      <c r="E137" t="n">
+        <v>950227</v>
+      </c>
+      <c r="F137" t="n">
+        <v>444184</v>
+      </c>
+      <c r="G137" t="n">
+        <v>46.75</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>194.43</v>
+      </c>
+      <c r="C138" t="n">
+        <v>194.43</v>
+      </c>
+      <c r="D138" t="n">
+        <v>194.43</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1739768</v>
+      </c>
+      <c r="F138" t="n">
+        <v>587949</v>
+      </c>
+      <c r="G138" t="n">
+        <v>33.79</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>191.84</v>
+      </c>
+      <c r="C139" t="n">
+        <v>191.84</v>
+      </c>
+      <c r="D139" t="n">
+        <v>191.84</v>
+      </c>
+      <c r="E139" t="n">
+        <v>633217</v>
+      </c>
+      <c r="F139" t="n">
+        <v>303604</v>
+      </c>
+      <c r="G139" t="n">
+        <v>47.95</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="C140" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="D140" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1333909</v>
+      </c>
+      <c r="F140" t="n">
+        <v>451164</v>
+      </c>
+      <c r="G140" t="n">
+        <v>33.82</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>192.41</v>
+      </c>
+      <c r="C141" t="n">
+        <v>192.41</v>
+      </c>
+      <c r="D141" t="n">
+        <v>192.41</v>
+      </c>
+      <c r="E141" t="n">
+        <v>660719</v>
+      </c>
+      <c r="F141" t="n">
+        <v>264569</v>
+      </c>
+      <c r="G141" t="n">
+        <v>40.04</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>192.3</v>
+      </c>
+      <c r="C142" t="n">
+        <v>192.3</v>
+      </c>
+      <c r="D142" t="n">
+        <v>192.3</v>
+      </c>
+      <c r="E142" t="n">
+        <v>472521</v>
+      </c>
+      <c r="F142" t="n">
+        <v>210132</v>
+      </c>
+      <c r="G142" t="n">
+        <v>44.47</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>192.63</v>
+      </c>
+      <c r="C143" t="n">
+        <v>192.63</v>
+      </c>
+      <c r="D143" t="n">
+        <v>192.63</v>
+      </c>
+      <c r="E143" t="n">
+        <v>434896</v>
+      </c>
+      <c r="F143" t="n">
+        <v>205008</v>
+      </c>
+      <c r="G143" t="n">
+        <v>47.14</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>187.85</v>
+      </c>
+      <c r="C144" t="n">
+        <v>187.85</v>
+      </c>
+      <c r="D144" t="n">
+        <v>187.85</v>
+      </c>
+      <c r="E144" t="n">
+        <v>443068</v>
+      </c>
+      <c r="F144" t="n">
+        <v>212871</v>
+      </c>
+      <c r="G144" t="n">
+        <v>48.04</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>189.3</v>
+      </c>
+      <c r="C145" t="n">
+        <v>189.3</v>
+      </c>
+      <c r="D145" t="n">
+        <v>189.3</v>
+      </c>
+      <c r="E145" t="n">
+        <v>456946</v>
+      </c>
+      <c r="F145" t="n">
+        <v>153022</v>
+      </c>
+      <c r="G145" t="n">
+        <v>33.49</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="C146" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>366125</v>
+      </c>
+      <c r="F146" t="n">
+        <v>167562</v>
+      </c>
+      <c r="G146" t="n">
+        <v>45.77</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>199.85</v>
+      </c>
+      <c r="C147" t="n">
+        <v>199.85</v>
+      </c>
+      <c r="D147" t="n">
+        <v>199.85</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1947287</v>
+      </c>
+      <c r="F147" t="n">
+        <v>667134</v>
+      </c>
+      <c r="G147" t="n">
+        <v>34.26</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="C148" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="D148" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="E148" t="n">
+        <v>930367</v>
+      </c>
+      <c r="F148" t="n">
+        <v>373801</v>
+      </c>
+      <c r="G148" t="n">
+        <v>40.18</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>197.26</v>
+      </c>
+      <c r="C149" t="n">
+        <v>197.26</v>
+      </c>
+      <c r="D149" t="n">
+        <v>197.26</v>
+      </c>
+      <c r="E149" t="n">
+        <v>872716</v>
+      </c>
+      <c r="F149" t="n">
+        <v>288873</v>
+      </c>
+      <c r="G149" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>198.25</v>
+      </c>
+      <c r="C150" t="n">
+        <v>198.25</v>
+      </c>
+      <c r="D150" t="n">
+        <v>198.25</v>
+      </c>
+      <c r="E150" t="n">
+        <v>702149</v>
+      </c>
+      <c r="F150" t="n">
+        <v>282416</v>
+      </c>
+      <c r="G150" t="n">
+        <v>40.22</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>194.73</v>
+      </c>
+      <c r="C151" t="n">
+        <v>194.73</v>
+      </c>
+      <c r="D151" t="n">
+        <v>194.73</v>
+      </c>
+      <c r="E151" t="n">
+        <v>777216</v>
+      </c>
+      <c r="F151" t="n">
+        <v>364022</v>
+      </c>
+      <c r="G151" t="n">
+        <v>46.84</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>193.96</v>
+      </c>
+      <c r="C152" t="n">
+        <v>193.96</v>
+      </c>
+      <c r="D152" t="n">
+        <v>193.96</v>
+      </c>
+      <c r="E152" t="n">
+        <v>733945</v>
+      </c>
+      <c r="F152" t="n">
+        <v>347611</v>
+      </c>
+      <c r="G152" t="n">
+        <v>47.36</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>188.08</v>
+      </c>
+      <c r="C153" t="n">
+        <v>188.08</v>
+      </c>
+      <c r="D153" t="n">
+        <v>188.08</v>
+      </c>
+      <c r="E153" t="n">
+        <v>472884</v>
+      </c>
+      <c r="F153" t="n">
+        <v>266288</v>
+      </c>
+      <c r="G153" t="n">
+        <v>56.31</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>187.09</v>
+      </c>
+      <c r="C154" t="n">
+        <v>187.09</v>
+      </c>
+      <c r="D154" t="n">
+        <v>187.09</v>
+      </c>
+      <c r="E154" t="n">
+        <v>844509</v>
+      </c>
+      <c r="F154" t="n">
+        <v>247100</v>
+      </c>
+      <c r="G154" t="n">
+        <v>29.26</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>184.41</v>
+      </c>
+      <c r="C155" t="n">
+        <v>184.41</v>
+      </c>
+      <c r="D155" t="n">
+        <v>184.41</v>
+      </c>
+      <c r="E155" t="n">
+        <v>831700</v>
+      </c>
+      <c r="F155" t="n">
+        <v>386046</v>
+      </c>
+      <c r="G155" t="n">
+        <v>46.42</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>183.21</v>
+      </c>
+      <c r="C156" t="n">
+        <v>183.21</v>
+      </c>
+      <c r="D156" t="n">
+        <v>183.21</v>
+      </c>
+      <c r="E156" t="n">
+        <v>482698</v>
+      </c>
+      <c r="F156" t="n">
+        <v>205279</v>
+      </c>
+      <c r="G156" t="n">
+        <v>42.53</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>193.99</v>
+      </c>
+      <c r="C157" t="n">
+        <v>193.99</v>
+      </c>
+      <c r="D157" t="n">
+        <v>193.99</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1254551</v>
+      </c>
+      <c r="F157" t="n">
+        <v>546403</v>
+      </c>
+      <c r="G157" t="n">
+        <v>43.55</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>189.06</v>
+      </c>
+      <c r="C158" t="n">
+        <v>189.06</v>
+      </c>
+      <c r="D158" t="n">
+        <v>189.06</v>
+      </c>
+      <c r="E158" t="n">
+        <v>523499</v>
+      </c>
+      <c r="F158" t="n">
+        <v>219186</v>
+      </c>
+      <c r="G158" t="n">
+        <v>41.87</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>190.05</v>
+      </c>
+      <c r="C159" t="n">
+        <v>190.05</v>
+      </c>
+      <c r="D159" t="n">
+        <v>190.05</v>
+      </c>
+      <c r="E159" t="n">
+        <v>424088</v>
+      </c>
+      <c r="F159" t="n">
+        <v>169010</v>
+      </c>
+      <c r="G159" t="n">
+        <v>39.85</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>192.75</v>
+      </c>
+      <c r="C160" t="n">
+        <v>192.75</v>
+      </c>
+      <c r="D160" t="n">
+        <v>192.75</v>
+      </c>
+      <c r="E160" t="n">
+        <v>444587</v>
+      </c>
+      <c r="F160" t="n">
+        <v>177892</v>
+      </c>
+      <c r="G160" t="n">
+        <v>40.01</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>187.53</v>
+      </c>
+      <c r="C161" t="n">
+        <v>187.53</v>
+      </c>
+      <c r="D161" t="n">
+        <v>187.53</v>
+      </c>
+      <c r="E161" t="n">
+        <v>413683</v>
+      </c>
+      <c r="F161" t="n">
+        <v>198764</v>
+      </c>
+      <c r="G161" t="n">
+        <v>48.05</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>185.31</v>
+      </c>
+      <c r="C162" t="n">
+        <v>185.31</v>
+      </c>
+      <c r="D162" t="n">
+        <v>185.31</v>
+      </c>
+      <c r="E162" t="n">
+        <v>390634</v>
+      </c>
+      <c r="F162" t="n">
+        <v>146661</v>
+      </c>
+      <c r="G162" t="n">
+        <v>37.54</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>185.89</v>
+      </c>
+      <c r="C163" t="n">
+        <v>185.89</v>
+      </c>
+      <c r="D163" t="n">
+        <v>185.89</v>
+      </c>
+      <c r="E163" t="n">
+        <v>294573</v>
+      </c>
+      <c r="F163" t="n">
+        <v>118026</v>
+      </c>
+      <c r="G163" t="n">
+        <v>40.07</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>188.38</v>
+      </c>
+      <c r="C164" t="n">
+        <v>188.38</v>
+      </c>
+      <c r="D164" t="n">
+        <v>188.38</v>
+      </c>
+      <c r="E164" t="n">
+        <v>383606</v>
+      </c>
+      <c r="F164" t="n">
+        <v>195892</v>
+      </c>
+      <c r="G164" t="n">
+        <v>51.07</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>184.08</v>
+      </c>
+      <c r="C165" t="n">
+        <v>184.08</v>
+      </c>
+      <c r="D165" t="n">
+        <v>184.08</v>
+      </c>
+      <c r="E165" t="n">
+        <v>330349</v>
+      </c>
+      <c r="F165" t="n">
+        <v>166260</v>
+      </c>
+      <c r="G165" t="n">
+        <v>50.33</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>185.49</v>
+      </c>
+      <c r="C166" t="n">
+        <v>185.49</v>
+      </c>
+      <c r="D166" t="n">
+        <v>185.49</v>
+      </c>
+      <c r="E166" t="n">
+        <v>539409</v>
+      </c>
+      <c r="F166" t="n">
+        <v>170183</v>
+      </c>
+      <c r="G166" t="n">
+        <v>31.55</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>185.27</v>
+      </c>
+      <c r="C167" t="n">
+        <v>185.27</v>
+      </c>
+      <c r="D167" t="n">
+        <v>185.27</v>
+      </c>
+      <c r="E167" t="n">
+        <v>235869</v>
+      </c>
+      <c r="F167" t="n">
+        <v>99661</v>
+      </c>
+      <c r="G167" t="n">
+        <v>42.25</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>188.24</v>
+      </c>
+      <c r="C168" t="n">
+        <v>188.24</v>
+      </c>
+      <c r="D168" t="n">
+        <v>188.24</v>
+      </c>
+      <c r="E168" t="n">
+        <v>338765</v>
+      </c>
+      <c r="F168" t="n">
+        <v>125191</v>
+      </c>
+      <c r="G168" t="n">
+        <v>36.96</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>184.32</v>
+      </c>
+      <c r="C169" t="n">
+        <v>184.32</v>
+      </c>
+      <c r="D169" t="n">
+        <v>184.32</v>
+      </c>
+      <c r="E169" t="n">
+        <v>343786</v>
+      </c>
+      <c r="F169" t="n">
+        <v>159428</v>
+      </c>
+      <c r="G169" t="n">
+        <v>46.37</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>185.55</v>
+      </c>
+      <c r="C170" t="n">
+        <v>185.55</v>
+      </c>
+      <c r="D170" t="n">
+        <v>185.55</v>
+      </c>
+      <c r="E170" t="n">
+        <v>296408</v>
+      </c>
+      <c r="F170" t="n">
+        <v>122961</v>
+      </c>
+      <c r="G170" t="n">
+        <v>41.48</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>181.37</v>
+      </c>
+      <c r="C171" t="n">
+        <v>181.37</v>
+      </c>
+      <c r="D171" t="n">
+        <v>181.37</v>
+      </c>
+      <c r="E171" t="n">
+        <v>820891</v>
+      </c>
+      <c r="F171" t="n">
+        <v>403772</v>
+      </c>
+      <c r="G171" t="n">
+        <v>49.19</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>187.45</v>
+      </c>
+      <c r="C172" t="n">
+        <v>187.45</v>
+      </c>
+      <c r="D172" t="n">
+        <v>187.45</v>
+      </c>
+      <c r="E172" t="n">
+        <v>541572</v>
+      </c>
+      <c r="F172" t="n">
+        <v>288116</v>
+      </c>
+      <c r="G172" t="n">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>189.46</v>
+      </c>
+      <c r="C173" t="n">
+        <v>189.46</v>
+      </c>
+      <c r="D173" t="n">
+        <v>189.46</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1217011</v>
+      </c>
+      <c r="F173" t="n">
+        <v>451513</v>
+      </c>
+      <c r="G173" t="n">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>187.85</v>
+      </c>
+      <c r="C174" t="n">
+        <v>187.85</v>
+      </c>
+      <c r="D174" t="n">
+        <v>187.85</v>
+      </c>
+      <c r="E174" t="n">
+        <v>546155</v>
+      </c>
+      <c r="F174" t="n">
+        <v>175352</v>
+      </c>
+      <c r="G174" t="n">
+        <v>32.11</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>187.7</v>
+      </c>
+      <c r="C175" t="n">
+        <v>187.7</v>
+      </c>
+      <c r="D175" t="n">
+        <v>187.7</v>
+      </c>
+      <c r="E175" t="n">
+        <v>321245</v>
+      </c>
+      <c r="F175" t="n">
+        <v>132116</v>
+      </c>
+      <c r="G175" t="n">
+        <v>41.13</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>188.92</v>
+      </c>
+      <c r="C176" t="n">
+        <v>188.92</v>
+      </c>
+      <c r="D176" t="n">
+        <v>188.92</v>
+      </c>
+      <c r="E176" t="n">
+        <v>339683</v>
+      </c>
+      <c r="F176" t="n">
+        <v>159487</v>
+      </c>
+      <c r="G176" t="n">
+        <v>46.95</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>187.37</v>
+      </c>
+      <c r="C177" t="n">
+        <v>187.37</v>
+      </c>
+      <c r="D177" t="n">
+        <v>187.37</v>
+      </c>
+      <c r="E177" t="n">
+        <v>273657</v>
+      </c>
+      <c r="F177" t="n">
+        <v>141968</v>
+      </c>
+      <c r="G177" t="n">
+        <v>51.88</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>182.92</v>
+      </c>
+      <c r="C178" t="n">
+        <v>182.92</v>
+      </c>
+      <c r="D178" t="n">
+        <v>182.92</v>
+      </c>
+      <c r="E178" t="n">
+        <v>326006</v>
+      </c>
+      <c r="F178" t="n">
+        <v>168247</v>
+      </c>
+      <c r="G178" t="n">
+        <v>51.61</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>173.72</v>
+      </c>
+      <c r="C179" t="n">
+        <v>173.72</v>
+      </c>
+      <c r="D179" t="n">
+        <v>173.72</v>
+      </c>
+      <c r="E179" t="n">
+        <v>654920</v>
+      </c>
+      <c r="F179" t="n">
+        <v>371642</v>
+      </c>
+      <c r="G179" t="n">
+        <v>56.75</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>175.43</v>
+      </c>
+      <c r="C180" t="n">
+        <v>175.43</v>
+      </c>
+      <c r="D180" t="n">
+        <v>175.43</v>
+      </c>
+      <c r="E180" t="n">
+        <v>545220</v>
+      </c>
+      <c r="F180" t="n">
+        <v>159581</v>
+      </c>
+      <c r="G180" t="n">
+        <v>29.27</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>176.88</v>
+      </c>
+      <c r="C181" t="n">
+        <v>176.88</v>
+      </c>
+      <c r="D181" t="n">
+        <v>176.88</v>
+      </c>
+      <c r="E181" t="n">
+        <v>265289</v>
+      </c>
+      <c r="F181" t="n">
+        <v>92921</v>
+      </c>
+      <c r="G181" t="n">
+        <v>35.03</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>175.86</v>
+      </c>
+      <c r="C182" t="n">
+        <v>175.86</v>
+      </c>
+      <c r="D182" t="n">
+        <v>175.86</v>
+      </c>
+      <c r="E182" t="n">
+        <v>236703</v>
+      </c>
+      <c r="F182" t="n">
+        <v>95526</v>
+      </c>
+      <c r="G182" t="n">
+        <v>40.36</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>171.97</v>
+      </c>
+      <c r="C183" t="n">
+        <v>171.97</v>
+      </c>
+      <c r="D183" t="n">
+        <v>171.97</v>
+      </c>
+      <c r="E183" t="n">
+        <v>363267</v>
+      </c>
+      <c r="F183" t="n">
+        <v>162324</v>
+      </c>
+      <c r="G183" t="n">
+        <v>44.68</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>168.61</v>
+      </c>
+      <c r="C184" t="n">
+        <v>168.61</v>
+      </c>
+      <c r="D184" t="n">
+        <v>168.61</v>
+      </c>
+      <c r="E184" t="n">
+        <v>208305</v>
+      </c>
+      <c r="F184" t="n">
+        <v>93470</v>
+      </c>
+      <c r="G184" t="n">
+        <v>44.87</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="C185" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="D185" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="E185" t="n">
+        <v>396684</v>
+      </c>
+      <c r="F185" t="n">
+        <v>191695</v>
+      </c>
+      <c r="G185" t="n">
+        <v>48.32</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>178.91</v>
+      </c>
+      <c r="C186" t="n">
+        <v>178.91</v>
+      </c>
+      <c r="D186" t="n">
+        <v>178.91</v>
+      </c>
+      <c r="E186" t="n">
+        <v>874345</v>
+      </c>
+      <c r="F186" t="n">
+        <v>395836</v>
+      </c>
+      <c r="G186" t="n">
+        <v>45.27</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>177.92</v>
+      </c>
+      <c r="C187" t="n">
+        <v>177.92</v>
+      </c>
+      <c r="D187" t="n">
+        <v>177.92</v>
+      </c>
+      <c r="E187" t="n">
+        <v>914123</v>
+      </c>
+      <c r="F187" t="n">
+        <v>317768</v>
+      </c>
+      <c r="G187" t="n">
+        <v>34.76</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>174.98</v>
+      </c>
+      <c r="C188" t="n">
+        <v>174.98</v>
+      </c>
+      <c r="D188" t="n">
+        <v>174.98</v>
+      </c>
+      <c r="E188" t="n">
+        <v>389139</v>
+      </c>
+      <c r="F188" t="n">
+        <v>184418</v>
+      </c>
+      <c r="G188" t="n">
+        <v>47.39</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>168.04</v>
+      </c>
+      <c r="C189" t="n">
+        <v>168.04</v>
+      </c>
+      <c r="D189" t="n">
+        <v>168.04</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2546904</v>
+      </c>
+      <c r="F189" t="n">
+        <v>629873</v>
+      </c>
+      <c r="G189" t="n">
+        <v>24.73</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>176.83</v>
+      </c>
+      <c r="C190" t="n">
+        <v>176.83</v>
+      </c>
+      <c r="D190" t="n">
+        <v>176.83</v>
+      </c>
+      <c r="E190" t="n">
+        <v>968096</v>
+      </c>
+      <c r="F190" t="n">
+        <v>360191</v>
+      </c>
+      <c r="G190" t="n">
+        <v>37.21</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>174.22</v>
+      </c>
+      <c r="C191" t="n">
+        <v>174.22</v>
+      </c>
+      <c r="D191" t="n">
+        <v>174.22</v>
+      </c>
+      <c r="E191" t="n">
+        <v>351344</v>
+      </c>
+      <c r="F191" t="n">
+        <v>143180</v>
+      </c>
+      <c r="G191" t="n">
+        <v>40.75</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>171.51</v>
+      </c>
+      <c r="C192" t="n">
+        <v>171.51</v>
+      </c>
+      <c r="D192" t="n">
+        <v>171.51</v>
+      </c>
+      <c r="E192" t="n">
+        <v>226625</v>
+      </c>
+      <c r="F192" t="n">
+        <v>105515</v>
+      </c>
+      <c r="G192" t="n">
+        <v>46.56</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>175.77</v>
+      </c>
+      <c r="C193" t="n">
+        <v>175.77</v>
+      </c>
+      <c r="D193" t="n">
+        <v>175.77</v>
+      </c>
+      <c r="E193" t="n">
+        <v>533111</v>
+      </c>
+      <c r="F193" t="n">
+        <v>249629</v>
+      </c>
+      <c r="G193" t="n">
+        <v>46.82</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>175.64</v>
+      </c>
+      <c r="C194" t="n">
+        <v>175.64</v>
+      </c>
+      <c r="D194" t="n">
+        <v>175.64</v>
+      </c>
+      <c r="E194" t="n">
+        <v>358755</v>
+      </c>
+      <c r="F194" t="n">
+        <v>169765</v>
+      </c>
+      <c r="G194" t="n">
+        <v>47.32</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="C195" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="D195" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="E195" t="n">
+        <v>340758</v>
+      </c>
+      <c r="F195" t="n">
+        <v>138068</v>
+      </c>
+      <c r="G195" t="n">
+        <v>40.52</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>177.04</v>
+      </c>
+      <c r="C196" t="n">
+        <v>177.04</v>
+      </c>
+      <c r="D196" t="n">
+        <v>177.04</v>
+      </c>
+      <c r="E196" t="n">
+        <v>260965</v>
+      </c>
+      <c r="F196" t="n">
+        <v>151649</v>
+      </c>
+      <c r="G196" t="n">
+        <v>58.11</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>176.12</v>
+      </c>
+      <c r="C197" t="n">
+        <v>176.12</v>
+      </c>
+      <c r="D197" t="n">
+        <v>176.12</v>
+      </c>
+      <c r="E197" t="n">
+        <v>352036</v>
+      </c>
+      <c r="F197" t="n">
+        <v>164844</v>
+      </c>
+      <c r="G197" t="n">
+        <v>46.83</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>175.85</v>
+      </c>
+      <c r="C198" t="n">
+        <v>175.85</v>
+      </c>
+      <c r="D198" t="n">
+        <v>175.85</v>
+      </c>
+      <c r="E198" t="n">
+        <v>240114</v>
+      </c>
+      <c r="F198" t="n">
+        <v>96815</v>
+      </c>
+      <c r="G198" t="n">
+        <v>40.32</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="C199" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D199" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E199" t="n">
+        <v>278945</v>
+      </c>
+      <c r="F199" t="n">
+        <v>123535</v>
+      </c>
+      <c r="G199" t="n">
+        <v>44.29</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>173.92</v>
+      </c>
+      <c r="C200" t="n">
+        <v>173.92</v>
+      </c>
+      <c r="D200" t="n">
+        <v>173.92</v>
+      </c>
+      <c r="E200" t="n">
+        <v>198800</v>
+      </c>
+      <c r="F200" t="n">
+        <v>96669</v>
+      </c>
+      <c r="G200" t="n">
+        <v>48.63</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>170.08</v>
+      </c>
+      <c r="C201" t="n">
+        <v>170.08</v>
+      </c>
+      <c r="D201" t="n">
+        <v>170.08</v>
+      </c>
+      <c r="E201" t="n">
+        <v>265406</v>
+      </c>
+      <c r="F201" t="n">
+        <v>122946</v>
+      </c>
+      <c r="G201" t="n">
+        <v>46.32</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>169.37</v>
+      </c>
+      <c r="C202" t="n">
+        <v>169.37</v>
+      </c>
+      <c r="D202" t="n">
+        <v>169.37</v>
+      </c>
+      <c r="E202" t="n">
+        <v>193347</v>
+      </c>
+      <c r="F202" t="n">
+        <v>79658</v>
+      </c>
+      <c r="G202" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>170.46</v>
+      </c>
+      <c r="C203" t="n">
+        <v>170.46</v>
+      </c>
+      <c r="D203" t="n">
+        <v>170.46</v>
+      </c>
+      <c r="E203" t="n">
+        <v>207394</v>
+      </c>
+      <c r="F203" t="n">
+        <v>92854</v>
+      </c>
+      <c r="G203" t="n">
+        <v>44.77</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>171.81</v>
+      </c>
+      <c r="C204" t="n">
+        <v>171.81</v>
+      </c>
+      <c r="D204" t="n">
+        <v>171.81</v>
+      </c>
+      <c r="E204" t="n">
+        <v>330590</v>
+      </c>
+      <c r="F204" t="n">
+        <v>139266</v>
+      </c>
+      <c r="G204" t="n">
+        <v>42.13</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>176.41</v>
+      </c>
+      <c r="C205" t="n">
+        <v>176.41</v>
+      </c>
+      <c r="D205" t="n">
+        <v>176.41</v>
+      </c>
+      <c r="E205" t="n">
+        <v>523019</v>
+      </c>
+      <c r="F205" t="n">
+        <v>286184</v>
+      </c>
+      <c r="G205" t="n">
+        <v>54.72</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>177.12</v>
+      </c>
+      <c r="C206" t="n">
+        <v>177.12</v>
+      </c>
+      <c r="D206" t="n">
+        <v>177.12</v>
+      </c>
+      <c r="E206" t="n">
+        <v>259434</v>
+      </c>
+      <c r="F206" t="n">
+        <v>148562</v>
+      </c>
+      <c r="G206" t="n">
+        <v>57.26</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>183.81</v>
+      </c>
+      <c r="C207" t="n">
+        <v>183.81</v>
+      </c>
+      <c r="D207" t="n">
+        <v>183.81</v>
+      </c>
+      <c r="E207" t="n">
+        <v>976602</v>
+      </c>
+      <c r="F207" t="n">
+        <v>433022</v>
+      </c>
+      <c r="G207" t="n">
+        <v>44.34</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>185.67</v>
+      </c>
+      <c r="C208" t="n">
+        <v>185.67</v>
+      </c>
+      <c r="D208" t="n">
+        <v>185.67</v>
+      </c>
+      <c r="E208" t="n">
+        <v>632913</v>
+      </c>
+      <c r="F208" t="n">
+        <v>274886</v>
+      </c>
+      <c r="G208" t="n">
+        <v>43.43</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>187.59</v>
+      </c>
+      <c r="C209" t="n">
+        <v>187.59</v>
+      </c>
+      <c r="D209" t="n">
+        <v>187.59</v>
+      </c>
+      <c r="E209" t="n">
+        <v>689380</v>
+      </c>
+      <c r="F209" t="n">
+        <v>311452</v>
+      </c>
+      <c r="G209" t="n">
+        <v>45.18</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>183.17</v>
+      </c>
+      <c r="C210" t="n">
+        <v>183.17</v>
+      </c>
+      <c r="D210" t="n">
+        <v>183.17</v>
+      </c>
+      <c r="E210" t="n">
+        <v>422229</v>
+      </c>
+      <c r="F210" t="n">
+        <v>217935</v>
+      </c>
+      <c r="G210" t="n">
+        <v>51.62</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>183.52</v>
+      </c>
+      <c r="C211" t="n">
+        <v>183.52</v>
+      </c>
+      <c r="D211" t="n">
+        <v>183.52</v>
+      </c>
+      <c r="E211" t="n">
+        <v>329084</v>
+      </c>
+      <c r="F211" t="n">
+        <v>143877</v>
+      </c>
+      <c r="G211" t="n">
+        <v>43.72</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>182.51</v>
+      </c>
+      <c r="C212" t="n">
+        <v>182.51</v>
+      </c>
+      <c r="D212" t="n">
+        <v>182.51</v>
+      </c>
+      <c r="E212" t="n">
+        <v>213344</v>
+      </c>
+      <c r="F212" t="n">
+        <v>112424</v>
+      </c>
+      <c r="G212" t="n">
+        <v>52.7</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>181.42</v>
+      </c>
+      <c r="C213" t="n">
+        <v>181.42</v>
+      </c>
+      <c r="D213" t="n">
+        <v>181.42</v>
+      </c>
+      <c r="E213" t="n">
+        <v>419687</v>
+      </c>
+      <c r="F213" t="n">
+        <v>231181</v>
+      </c>
+      <c r="G213" t="n">
+        <v>55.08</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>186.72</v>
+      </c>
+      <c r="C214" t="n">
+        <v>186.72</v>
+      </c>
+      <c r="D214" t="n">
+        <v>186.72</v>
+      </c>
+      <c r="E214" t="n">
+        <v>550308</v>
+      </c>
+      <c r="F214" t="n">
+        <v>260604</v>
+      </c>
+      <c r="G214" t="n">
+        <v>47.36</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="C215" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="D215" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="E215" t="n">
+        <v>4067415</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1372117</v>
+      </c>
+      <c r="G215" t="n">
+        <v>33.73</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>198.59</v>
+      </c>
+      <c r="C216" t="n">
+        <v>198.59</v>
+      </c>
+      <c r="D216" t="n">
+        <v>198.59</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2468915</v>
+      </c>
+      <c r="F216" t="n">
+        <v>959607</v>
+      </c>
+      <c r="G216" t="n">
+        <v>38.87</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>200.64</v>
+      </c>
+      <c r="C217" t="n">
+        <v>200.64</v>
+      </c>
+      <c r="D217" t="n">
+        <v>200.64</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1633160</v>
+      </c>
+      <c r="F217" t="n">
+        <v>672643</v>
+      </c>
+      <c r="G217" t="n">
+        <v>41.19</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>203.59</v>
+      </c>
+      <c r="C218" t="n">
+        <v>203.59</v>
+      </c>
+      <c r="D218" t="n">
+        <v>203.59</v>
+      </c>
+      <c r="E218" t="n">
+        <v>2148632</v>
+      </c>
+      <c r="F218" t="n">
+        <v>905286</v>
+      </c>
+      <c r="G218" t="n">
+        <v>42.13</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>203.42</v>
+      </c>
+      <c r="C219" t="n">
+        <v>203.42</v>
+      </c>
+      <c r="D219" t="n">
+        <v>203.42</v>
+      </c>
+      <c r="E219" t="n">
+        <v>869077</v>
+      </c>
+      <c r="F219" t="n">
+        <v>364802</v>
+      </c>
+      <c r="G219" t="n">
+        <v>41.98</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>197.55</v>
+      </c>
+      <c r="C220" t="n">
+        <v>197.55</v>
+      </c>
+      <c r="D220" t="n">
+        <v>197.55</v>
+      </c>
+      <c r="E220" t="n">
+        <v>912759</v>
+      </c>
+      <c r="F220" t="n">
+        <v>420780</v>
+      </c>
+      <c r="G220" t="n">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>194.36</v>
+      </c>
+      <c r="C221" t="n">
+        <v>194.36</v>
+      </c>
+      <c r="D221" t="n">
+        <v>194.36</v>
+      </c>
+      <c r="E221" t="n">
+        <v>601715</v>
+      </c>
+      <c r="F221" t="n">
+        <v>253461</v>
+      </c>
+      <c r="G221" t="n">
+        <v>42.12</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>189.53</v>
+      </c>
+      <c r="C222" t="n">
+        <v>189.53</v>
+      </c>
+      <c r="D222" t="n">
+        <v>189.53</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1172422</v>
+      </c>
+      <c r="F222" t="n">
+        <v>483530</v>
+      </c>
+      <c r="G222" t="n">
+        <v>41.24</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="C223" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="D223" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="E223" t="n">
+        <v>644859</v>
+      </c>
+      <c r="F223" t="n">
+        <v>266491</v>
+      </c>
+      <c r="G223" t="n">
+        <v>41.33</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>186.29</v>
+      </c>
+      <c r="C224" t="n">
+        <v>186.29</v>
+      </c>
+      <c r="D224" t="n">
+        <v>186.29</v>
+      </c>
+      <c r="E224" t="n">
+        <v>421618</v>
+      </c>
+      <c r="F224" t="n">
+        <v>205684</v>
+      </c>
+      <c r="G224" t="n">
+        <v>48.78</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>194.9</v>
+      </c>
+      <c r="C225" t="n">
+        <v>194.9</v>
+      </c>
+      <c r="D225" t="n">
+        <v>194.9</v>
+      </c>
+      <c r="E225" t="n">
+        <v>627319</v>
+      </c>
+      <c r="F225" t="n">
+        <v>286118</v>
+      </c>
+      <c r="G225" t="n">
+        <v>45.61</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>201.84</v>
+      </c>
+      <c r="C226" t="n">
+        <v>201.84</v>
+      </c>
+      <c r="D226" t="n">
+        <v>201.84</v>
+      </c>
+      <c r="E226" t="n">
+        <v>1025325</v>
+      </c>
+      <c r="F226" t="n">
+        <v>462832</v>
+      </c>
+      <c r="G226" t="n">
+        <v>45.14</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>202.29</v>
+      </c>
+      <c r="C227" t="n">
+        <v>202.29</v>
+      </c>
+      <c r="D227" t="n">
+        <v>202.29</v>
+      </c>
+      <c r="E227" t="n">
+        <v>683905</v>
+      </c>
+      <c r="F227" t="n">
+        <v>341393</v>
+      </c>
+      <c r="G227" t="n">
+        <v>49.92</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="C228" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="D228" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="E228" t="n">
+        <v>687037</v>
+      </c>
+      <c r="F228" t="n">
+        <v>365411</v>
+      </c>
+      <c r="G228" t="n">
+        <v>53.19</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>215.49</v>
+      </c>
+      <c r="C229" t="n">
+        <v>215.49</v>
+      </c>
+      <c r="D229" t="n">
+        <v>215.49</v>
+      </c>
+      <c r="E229" t="n">
+        <v>6910783</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1737780</v>
+      </c>
+      <c r="G229" t="n">
+        <v>25.15</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>214.28</v>
+      </c>
+      <c r="C230" t="n">
+        <v>214.28</v>
+      </c>
+      <c r="D230" t="n">
+        <v>214.28</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1412309</v>
+      </c>
+      <c r="F230" t="n">
+        <v>463861</v>
+      </c>
+      <c r="G230" t="n">
+        <v>32.84</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>216.04</v>
+      </c>
+      <c r="C231" t="n">
+        <v>216.04</v>
+      </c>
+      <c r="D231" t="n">
+        <v>216.04</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1245710</v>
+      </c>
+      <c r="F231" t="n">
+        <v>505539</v>
+      </c>
+      <c r="G231" t="n">
+        <v>40.58</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>216.43</v>
+      </c>
+      <c r="C232" t="n">
+        <v>216.43</v>
+      </c>
+      <c r="D232" t="n">
+        <v>216.43</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1048669</v>
+      </c>
+      <c r="F232" t="n">
+        <v>404950</v>
+      </c>
+      <c r="G232" t="n">
+        <v>38.62</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>208.98</v>
+      </c>
+      <c r="C233" t="n">
+        <v>208.98</v>
+      </c>
+      <c r="D233" t="n">
+        <v>208.98</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1159136</v>
+      </c>
+      <c r="F233" t="n">
+        <v>509723</v>
+      </c>
+      <c r="G233" t="n">
+        <v>43.97</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>213.32</v>
+      </c>
+      <c r="C234" t="n">
+        <v>213.32</v>
+      </c>
+      <c r="D234" t="n">
+        <v>213.32</v>
+      </c>
+      <c r="E234" t="n">
+        <v>731603</v>
+      </c>
+      <c r="F234" t="n">
+        <v>302343</v>
+      </c>
+      <c r="G234" t="n">
+        <v>41.33</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>215.14</v>
+      </c>
+      <c r="C235" t="n">
+        <v>215.14</v>
+      </c>
+      <c r="D235" t="n">
+        <v>215.14</v>
+      </c>
+      <c r="E235" t="n">
+        <v>850074</v>
+      </c>
+      <c r="F235" t="n">
+        <v>371710</v>
+      </c>
+      <c r="G235" t="n">
+        <v>43.73</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>202.36</v>
+      </c>
+      <c r="C236" t="n">
+        <v>202.36</v>
+      </c>
+      <c r="D236" t="n">
+        <v>202.36</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1149186</v>
+      </c>
+      <c r="F236" t="n">
+        <v>658231</v>
+      </c>
+      <c r="G236" t="n">
+        <v>57.28</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>198.67</v>
+      </c>
+      <c r="C237" t="n">
+        <v>198.67</v>
+      </c>
+      <c r="D237" t="n">
+        <v>198.67</v>
+      </c>
+      <c r="E237" t="n">
+        <v>810360</v>
+      </c>
+      <c r="F237" t="n">
+        <v>377747</v>
+      </c>
+      <c r="G237" t="n">
+        <v>46.61</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>205.68</v>
+      </c>
+      <c r="C238" t="n">
+        <v>205.68</v>
+      </c>
+      <c r="D238" t="n">
+        <v>205.68</v>
+      </c>
+      <c r="E238" t="n">
+        <v>294769</v>
+      </c>
+      <c r="F238" t="n">
+        <v>130862</v>
+      </c>
+      <c r="G238" t="n">
+        <v>44.39</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>203.62</v>
+      </c>
+      <c r="C239" t="n">
+        <v>203.62</v>
+      </c>
+      <c r="D239" t="n">
+        <v>203.62</v>
+      </c>
+      <c r="E239" t="n">
+        <v>699579</v>
+      </c>
+      <c r="F239" t="n">
+        <v>319983</v>
+      </c>
+      <c r="G239" t="n">
+        <v>45.74</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>202.06</v>
+      </c>
+      <c r="C240" t="n">
+        <v>202.06</v>
+      </c>
+      <c r="D240" t="n">
+        <v>202.06</v>
+      </c>
+      <c r="E240" t="n">
+        <v>496337</v>
+      </c>
+      <c r="F240" t="n">
+        <v>260629</v>
+      </c>
+      <c r="G240" t="n">
+        <v>52.51</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>203.64</v>
+      </c>
+      <c r="C241" t="n">
+        <v>203.64</v>
+      </c>
+      <c r="D241" t="n">
+        <v>203.64</v>
+      </c>
+      <c r="E241" t="n">
+        <v>631297</v>
+      </c>
+      <c r="F241" t="n">
+        <v>312847</v>
+      </c>
+      <c r="G241" t="n">
+        <v>49.56</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>206.17</v>
+      </c>
+      <c r="C242" t="n">
+        <v>206.17</v>
+      </c>
+      <c r="D242" t="n">
+        <v>206.17</v>
+      </c>
+      <c r="E242" t="n">
+        <v>1088174</v>
+      </c>
+      <c r="F242" t="n">
+        <v>541487</v>
+      </c>
+      <c r="G242" t="n">
+        <v>49.76</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>212.67</v>
+      </c>
+      <c r="C243" t="n">
+        <v>212.67</v>
+      </c>
+      <c r="D243" t="n">
+        <v>212.67</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1257544</v>
+      </c>
+      <c r="F243" t="n">
+        <v>645601</v>
+      </c>
+      <c r="G243" t="n">
+        <v>51.34</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>213.28</v>
+      </c>
+      <c r="C244" t="n">
+        <v>213.28</v>
+      </c>
+      <c r="D244" t="n">
+        <v>213.28</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1335699</v>
+      </c>
+      <c r="F244" t="n">
+        <v>525740</v>
+      </c>
+      <c r="G244" t="n">
+        <v>39.36</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>214.61</v>
+      </c>
+      <c r="C245" t="n">
+        <v>214.61</v>
+      </c>
+      <c r="D245" t="n">
+        <v>214.61</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1037028</v>
+      </c>
+      <c r="F245" t="n">
+        <v>452173</v>
+      </c>
+      <c r="G245" t="n">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>217.84</v>
+      </c>
+      <c r="C246" t="n">
+        <v>217.84</v>
+      </c>
+      <c r="D246" t="n">
+        <v>217.84</v>
+      </c>
+      <c r="E246" t="n">
+        <v>4247021</v>
+      </c>
+      <c r="F246" t="n">
+        <v>1379981</v>
+      </c>
+      <c r="G246" t="n">
+        <v>32.49</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="C247" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="D247" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1136428</v>
+      </c>
+      <c r="F247" t="n">
+        <v>520564</v>
+      </c>
+      <c r="G247" t="n">
+        <v>45.81</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>216.44</v>
+      </c>
+      <c r="C248" t="n">
+        <v>216.44</v>
+      </c>
+      <c r="D248" t="n">
+        <v>216.44</v>
+      </c>
+      <c r="E248" t="n">
+        <v>841439</v>
+      </c>
+      <c r="F248" t="n">
+        <v>366878</v>
+      </c>
+      <c r="G248" t="n">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>214.79</v>
+      </c>
+      <c r="C249" t="n">
+        <v>214.79</v>
+      </c>
+      <c r="D249" t="n">
+        <v>214.79</v>
+      </c>
+      <c r="E249" t="n">
+        <v>617710</v>
+      </c>
+      <c r="F249" t="n">
+        <v>263559</v>
+      </c>
+      <c r="G249" t="n">
+        <v>42.67</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>224.15</v>
+      </c>
+      <c r="C250" t="n">
+        <v>224.15</v>
+      </c>
+      <c r="D250" t="n">
+        <v>224.15</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1555566</v>
+      </c>
+      <c r="F250" t="n">
+        <v>861194</v>
+      </c>
+      <c r="G250" t="n">
+        <v>55.36</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>228.72</v>
+      </c>
+      <c r="C251" t="n">
+        <v>228.72</v>
+      </c>
+      <c r="D251" t="n">
+        <v>228.72</v>
+      </c>
+      <c r="E251" t="n">
+        <v>2476834</v>
+      </c>
+      <c r="F251" t="n">
+        <v>1124749</v>
+      </c>
+      <c r="G251" t="n">
+        <v>45.41</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>238.21</v>
+      </c>
+      <c r="C252" t="n">
+        <v>238.21</v>
+      </c>
+      <c r="D252" t="n">
+        <v>238.21</v>
+      </c>
+      <c r="E252" t="n">
+        <v>2948023</v>
+      </c>
+      <c r="F252" t="n">
+        <v>1509580</v>
+      </c>
+      <c r="G252" t="n">
+        <v>51.21</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>227.81</v>
+      </c>
+      <c r="C253" t="n">
+        <v>227.81</v>
+      </c>
+      <c r="D253" t="n">
+        <v>227.81</v>
+      </c>
+      <c r="E253" t="n">
+        <v>2451087</v>
+      </c>
+      <c r="F253" t="n">
+        <v>1237862</v>
+      </c>
+      <c r="G253" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>229.08</v>
+      </c>
+      <c r="C254" t="n">
+        <v>229.08</v>
+      </c>
+      <c r="D254" t="n">
+        <v>229.08</v>
+      </c>
+      <c r="E254" t="n">
+        <v>2480648</v>
+      </c>
+      <c r="F254" t="n">
+        <v>1154154</v>
+      </c>
+      <c r="G254" t="n">
+        <v>46.53</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>231.14</v>
+      </c>
+      <c r="C255" t="n">
+        <v>231.14</v>
+      </c>
+      <c r="D255" t="n">
+        <v>231.14</v>
+      </c>
+      <c r="E255" t="n">
+        <v>2886632</v>
+      </c>
+      <c r="F255" t="n">
+        <v>1282376</v>
+      </c>
+      <c r="G255" t="n">
+        <v>44.42</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>247.56</v>
+      </c>
+      <c r="C256" t="n">
+        <v>247.56</v>
+      </c>
+      <c r="D256" t="n">
+        <v>247.56</v>
+      </c>
+      <c r="E256" t="n">
+        <v>9154480</v>
+      </c>
+      <c r="F256" t="n">
+        <v>3022703</v>
+      </c>
+      <c r="G256" t="n">
+        <v>33.02</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>252</v>
+      </c>
+      <c r="C257" t="n">
+        <v>252</v>
+      </c>
+      <c r="D257" t="n">
+        <v>252</v>
+      </c>
+      <c r="E257" t="n">
+        <v>9066508</v>
+      </c>
+      <c r="F257" t="n">
+        <v>2604658</v>
+      </c>
+      <c r="G257" t="n">
+        <v>28.73</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>239.62</v>
+      </c>
+      <c r="C258" t="n">
+        <v>239.62</v>
+      </c>
+      <c r="D258" t="n">
+        <v>239.62</v>
+      </c>
+      <c r="E258" t="n">
+        <v>3552069</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1158078</v>
+      </c>
+      <c r="G258" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>238.73</v>
+      </c>
+      <c r="C259" t="n">
+        <v>238.73</v>
+      </c>
+      <c r="D259" t="n">
+        <v>238.73</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1735545</v>
+      </c>
+      <c r="F259" t="n">
+        <v>514624</v>
+      </c>
+      <c r="G259" t="n">
+        <v>29.65</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>221.99</v>
+      </c>
+      <c r="C260" t="n">
+        <v>221.99</v>
+      </c>
+      <c r="D260" t="n">
+        <v>221.99</v>
+      </c>
+      <c r="E260" t="n">
+        <v>1929671</v>
+      </c>
+      <c r="F260" t="n">
+        <v>810136</v>
+      </c>
+      <c r="G260" t="n">
+        <v>41.98</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>221.96</v>
+      </c>
+      <c r="C261" t="n">
+        <v>221.96</v>
+      </c>
+      <c r="D261" t="n">
+        <v>221.96</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1642377</v>
+      </c>
+      <c r="F261" t="n">
+        <v>639200</v>
+      </c>
+      <c r="G261" t="n">
+        <v>38.92</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="C262" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="D262" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1071708</v>
+      </c>
+      <c r="F262" t="n">
+        <v>514162</v>
+      </c>
+      <c r="G262" t="n">
+        <v>47.98</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>226.39</v>
+      </c>
+      <c r="C263" t="n">
+        <v>226.39</v>
+      </c>
+      <c r="D263" t="n">
+        <v>226.39</v>
+      </c>
+      <c r="E263" t="n">
+        <v>3780583</v>
+      </c>
+      <c r="F263" t="n">
+        <v>1075410</v>
+      </c>
+      <c r="G263" t="n">
+        <v>28.45</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>223.46</v>
+      </c>
+      <c r="C264" t="n">
+        <v>223.46</v>
+      </c>
+      <c r="D264" t="n">
+        <v>223.46</v>
+      </c>
+      <c r="E264" t="n">
+        <v>1211340</v>
+      </c>
+      <c r="F264" t="n">
+        <v>600124</v>
+      </c>
+      <c r="G264" t="n">
+        <v>49.54</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>221.41</v>
+      </c>
+      <c r="C265" t="n">
+        <v>221.41</v>
+      </c>
+      <c r="D265" t="n">
+        <v>221.41</v>
+      </c>
+      <c r="E265" t="n">
+        <v>891227</v>
+      </c>
+      <c r="F265" t="n">
+        <v>357731</v>
+      </c>
+      <c r="G265" t="n">
+        <v>40.14</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>216.12</v>
+      </c>
+      <c r="C266" t="n">
+        <v>216.12</v>
+      </c>
+      <c r="D266" t="n">
+        <v>216.12</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1175482</v>
+      </c>
+      <c r="F266" t="n">
+        <v>549090</v>
+      </c>
+      <c r="G266" t="n">
+        <v>46.71</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>212.63</v>
+      </c>
+      <c r="C267" t="n">
+        <v>212.63</v>
+      </c>
+      <c r="D267" t="n">
+        <v>212.63</v>
+      </c>
+      <c r="E267" t="n">
+        <v>979077</v>
+      </c>
+      <c r="F267" t="n">
+        <v>519602</v>
+      </c>
+      <c r="G267" t="n">
+        <v>53.07</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>207.43</v>
+      </c>
+      <c r="C268" t="n">
+        <v>207.43</v>
+      </c>
+      <c r="D268" t="n">
+        <v>207.43</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1548561</v>
+      </c>
+      <c r="F268" t="n">
+        <v>803047</v>
+      </c>
+      <c r="G268" t="n">
+        <v>51.86</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>199.7</v>
+      </c>
+      <c r="C269" t="n">
+        <v>199.7</v>
+      </c>
+      <c r="D269" t="n">
+        <v>199.7</v>
+      </c>
+      <c r="E269" t="n">
+        <v>2136594</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1172219</v>
+      </c>
+      <c r="G269" t="n">
+        <v>54.86</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>195.19</v>
+      </c>
+      <c r="C270" t="n">
+        <v>195.19</v>
+      </c>
+      <c r="D270" t="n">
+        <v>195.19</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1516493</v>
+      </c>
+      <c r="F270" t="n">
+        <v>683304</v>
+      </c>
+      <c r="G270" t="n">
+        <v>45.06</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>203.51</v>
+      </c>
+      <c r="C271" t="n">
+        <v>203.51</v>
+      </c>
+      <c r="D271" t="n">
+        <v>203.51</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1253435</v>
+      </c>
+      <c r="F271" t="n">
+        <v>408181</v>
+      </c>
+      <c r="G271" t="n">
+        <v>32.56</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>200.69</v>
+      </c>
+      <c r="C272" t="n">
+        <v>200.69</v>
+      </c>
+      <c r="D272" t="n">
+        <v>200.69</v>
+      </c>
+      <c r="E272" t="n">
+        <v>717920</v>
+      </c>
+      <c r="F272" t="n">
+        <v>325534</v>
+      </c>
+      <c r="G272" t="n">
+        <v>45.34</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>205.92</v>
+      </c>
+      <c r="C273" t="n">
+        <v>205.92</v>
+      </c>
+      <c r="D273" t="n">
+        <v>205.92</v>
+      </c>
+      <c r="E273" t="n">
+        <v>860520</v>
+      </c>
+      <c r="F273" t="n">
+        <v>300694</v>
+      </c>
+      <c r="G273" t="n">
+        <v>34.94</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>209.68</v>
+      </c>
+      <c r="C274" t="n">
+        <v>209.68</v>
+      </c>
+      <c r="D274" t="n">
+        <v>209.68</v>
+      </c>
+      <c r="E274" t="n">
+        <v>957812</v>
+      </c>
+      <c r="F274" t="n">
+        <v>443640</v>
+      </c>
+      <c r="G274" t="n">
+        <v>46.32</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>210.68</v>
+      </c>
+      <c r="C275" t="n">
+        <v>210.68</v>
+      </c>
+      <c r="D275" t="n">
+        <v>210.68</v>
+      </c>
+      <c r="E275" t="n">
+        <v>572740</v>
+      </c>
+      <c r="F275" t="n">
+        <v>238535</v>
+      </c>
+      <c r="G275" t="n">
+        <v>41.65</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>210.68</v>
+      </c>
+      <c r="C276" t="n">
+        <v>210.68</v>
+      </c>
+      <c r="D276" t="n">
+        <v>210.68</v>
+      </c>
+      <c r="E276" t="n">
+        <v>507420</v>
+      </c>
+      <c r="F276" t="n">
+        <v>208445</v>
+      </c>
+      <c r="G276" t="n">
+        <v>41.08</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="C277" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="D277" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="E277" t="n">
+        <v>755622</v>
+      </c>
+      <c r="F277" t="n">
+        <v>267538</v>
+      </c>
+      <c r="G277" t="n">
+        <v>35.41</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>209.36</v>
+      </c>
+      <c r="C278" t="n">
+        <v>209.36</v>
+      </c>
+      <c r="D278" t="n">
+        <v>209.36</v>
+      </c>
+      <c r="E278" t="n">
+        <v>516336</v>
+      </c>
+      <c r="F278" t="n">
+        <v>215723</v>
+      </c>
+      <c r="G278" t="n">
+        <v>41.78</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>210.32</v>
+      </c>
+      <c r="C279" t="n">
+        <v>210.32</v>
+      </c>
+      <c r="D279" t="n">
+        <v>210.32</v>
+      </c>
+      <c r="E279" t="n">
+        <v>611341</v>
+      </c>
+      <c r="F279" t="n">
+        <v>276297</v>
+      </c>
+      <c r="G279" t="n">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>218.33</v>
+      </c>
+      <c r="C280" t="n">
+        <v>218.33</v>
+      </c>
+      <c r="D280" t="n">
+        <v>218.33</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1670306</v>
+      </c>
+      <c r="F280" t="n">
+        <v>842957</v>
+      </c>
+      <c r="G280" t="n">
+        <v>50.47</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>216.68</v>
+      </c>
+      <c r="C281" t="n">
+        <v>216.68</v>
+      </c>
+      <c r="D281" t="n">
+        <v>216.68</v>
+      </c>
+      <c r="E281" t="n">
+        <v>751785</v>
+      </c>
+      <c r="F281" t="n">
+        <v>350337</v>
+      </c>
+      <c r="G281" t="n">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>213.86</v>
+      </c>
+      <c r="C282" t="n">
+        <v>213.86</v>
+      </c>
+      <c r="D282" t="n">
+        <v>213.86</v>
+      </c>
+      <c r="E282" t="n">
+        <v>430662</v>
+      </c>
+      <c r="F282" t="n">
+        <v>239231</v>
+      </c>
+      <c r="G282" t="n">
+        <v>55.55</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>213.54</v>
+      </c>
+      <c r="C283" t="n">
+        <v>213.54</v>
+      </c>
+      <c r="D283" t="n">
+        <v>213.54</v>
+      </c>
+      <c r="E283" t="n">
+        <v>488886</v>
+      </c>
+      <c r="F283" t="n">
+        <v>239880</v>
+      </c>
+      <c r="G283" t="n">
+        <v>49.07</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>209.28</v>
+      </c>
+      <c r="C284" t="n">
+        <v>209.28</v>
+      </c>
+      <c r="D284" t="n">
+        <v>209.28</v>
+      </c>
+      <c r="E284" t="n">
+        <v>355232</v>
+      </c>
+      <c r="F284" t="n">
+        <v>196485</v>
+      </c>
+      <c r="G284" t="n">
+        <v>55.31</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="C285" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="D285" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="E285" t="n">
+        <v>716611</v>
+      </c>
+      <c r="F285" t="n">
+        <v>378643</v>
+      </c>
+      <c r="G285" t="n">
+        <v>52.84</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>208.54</v>
+      </c>
+      <c r="C286" t="n">
+        <v>208.54</v>
+      </c>
+      <c r="D286" t="n">
+        <v>208.54</v>
+      </c>
+      <c r="E286" t="n">
+        <v>474989</v>
+      </c>
+      <c r="F286" t="n">
+        <v>272827</v>
+      </c>
+      <c r="G286" t="n">
+        <v>57.44</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>208.38</v>
+      </c>
+      <c r="C287" t="n">
+        <v>208.38</v>
+      </c>
+      <c r="D287" t="n">
+        <v>208.38</v>
+      </c>
+      <c r="E287" t="n">
+        <v>397312</v>
+      </c>
+      <c r="F287" t="n">
+        <v>206774</v>
+      </c>
+      <c r="G287" t="n">
+        <v>52.04</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>210.49</v>
+      </c>
+      <c r="C288" t="n">
+        <v>210.49</v>
+      </c>
+      <c r="D288" t="n">
+        <v>210.49</v>
+      </c>
+      <c r="E288" t="n">
+        <v>519743</v>
+      </c>
+      <c r="F288" t="n">
+        <v>276796</v>
+      </c>
+      <c r="G288" t="n">
+        <v>53.26</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>206.94</v>
+      </c>
+      <c r="C289" t="n">
+        <v>206.94</v>
+      </c>
+      <c r="D289" t="n">
+        <v>206.94</v>
+      </c>
+      <c r="E289" t="n">
+        <v>527547</v>
+      </c>
+      <c r="F289" t="n">
+        <v>263643</v>
+      </c>
+      <c r="G289" t="n">
+        <v>49.98</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>206.93</v>
+      </c>
+      <c r="C290" t="n">
+        <v>206.93</v>
+      </c>
+      <c r="D290" t="n">
+        <v>206.93</v>
+      </c>
+      <c r="E290" t="n">
+        <v>387550</v>
+      </c>
+      <c r="F290" t="n">
+        <v>161867</v>
+      </c>
+      <c r="G290" t="n">
+        <v>41.77</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>209.08</v>
+      </c>
+      <c r="C291" t="n">
+        <v>209.08</v>
+      </c>
+      <c r="D291" t="n">
+        <v>209.08</v>
+      </c>
+      <c r="E291" t="n">
+        <v>334428</v>
+      </c>
+      <c r="F291" t="n">
+        <v>161122</v>
+      </c>
+      <c r="G291" t="n">
+        <v>48.18</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>199.95</v>
+      </c>
+      <c r="C292" t="n">
+        <v>199.95</v>
+      </c>
+      <c r="D292" t="n">
+        <v>199.95</v>
+      </c>
+      <c r="E292" t="n">
+        <v>893761</v>
+      </c>
+      <c r="F292" t="n">
+        <v>492934</v>
+      </c>
+      <c r="G292" t="n">
+        <v>55.15</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="C293" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="D293" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="E293" t="n">
+        <v>991803</v>
+      </c>
+      <c r="F293" t="n">
+        <v>384138</v>
+      </c>
+      <c r="G293" t="n">
+        <v>38.73</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>192.49</v>
+      </c>
+      <c r="C294" t="n">
+        <v>192.49</v>
+      </c>
+      <c r="D294" t="n">
+        <v>192.49</v>
+      </c>
+      <c r="E294" t="n">
+        <v>724809</v>
+      </c>
+      <c r="F294" t="n">
+        <v>285906</v>
+      </c>
+      <c r="G294" t="n">
+        <v>39.45</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>190.05</v>
+      </c>
+      <c r="C295" t="n">
+        <v>190.05</v>
+      </c>
+      <c r="D295" t="n">
+        <v>190.05</v>
+      </c>
+      <c r="E295" t="n">
+        <v>447390</v>
+      </c>
+      <c r="F295" t="n">
+        <v>203654</v>
+      </c>
+      <c r="G295" t="n">
+        <v>45.52</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>192.57</v>
+      </c>
+      <c r="C296" t="n">
+        <v>192.57</v>
+      </c>
+      <c r="D296" t="n">
+        <v>192.57</v>
+      </c>
+      <c r="E296" t="n">
+        <v>449490</v>
+      </c>
+      <c r="F296" t="n">
+        <v>188757</v>
+      </c>
+      <c r="G296" t="n">
+        <v>41.99</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>192.57</v>
+      </c>
+      <c r="C297" t="n">
+        <v>192.57</v>
+      </c>
+      <c r="D297" t="n">
+        <v>192.57</v>
+      </c>
+      <c r="E297" t="n">
+        <v>449490</v>
+      </c>
+      <c r="F297" t="n">
+        <v>188757</v>
+      </c>
+      <c r="G297" t="n">
+        <v>41.99</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>193.73</v>
+      </c>
+      <c r="C298" t="n">
+        <v>193.73</v>
+      </c>
+      <c r="D298" t="n">
+        <v>193.73</v>
+      </c>
+      <c r="E298" t="n">
+        <v>409145</v>
+      </c>
+      <c r="F298" t="n">
+        <v>204113</v>
+      </c>
+      <c r="G298" t="n">
+        <v>49.89</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>205.68</v>
+      </c>
+      <c r="C299" t="n">
+        <v>205.68</v>
+      </c>
+      <c r="D299" t="n">
+        <v>205.68</v>
+      </c>
+      <c r="E299" t="n">
+        <v>2376238</v>
+      </c>
+      <c r="F299" t="n">
+        <v>799205</v>
+      </c>
+      <c r="G299" t="n">
+        <v>33.63</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>199.43</v>
+      </c>
+      <c r="C300" t="n">
+        <v>199.43</v>
+      </c>
+      <c r="D300" t="n">
+        <v>199.43</v>
+      </c>
+      <c r="E300" t="n">
+        <v>894187</v>
+      </c>
+      <c r="F300" t="n">
+        <v>407786</v>
+      </c>
+      <c r="G300" t="n">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>193.98</v>
+      </c>
+      <c r="C301" t="n">
+        <v>193.98</v>
+      </c>
+      <c r="D301" t="n">
+        <v>193.98</v>
+      </c>
+      <c r="E301" t="n">
+        <v>681135</v>
+      </c>
+      <c r="F301" t="n">
+        <v>260617</v>
+      </c>
+      <c r="G301" t="n">
+        <v>38.26</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B302" t="n">
         <v>201.17</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C302" t="n">
+        <v>201.17</v>
+      </c>
+      <c r="D302" t="n">
+        <v>201.17</v>
+      </c>
+      <c r="E302" t="n">
         <v>364240</v>
       </c>
-      <c r="D56" t="n">
+      <c r="F302" t="n">
         <v>171120</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G302" t="n">
         <v>46.98</v>
       </c>
     </row>
